--- a/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
+++ b/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7826A3-323F-45EE-868D-271BC53A753D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45E6336-AC6C-4183-85D6-0B29325654B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="37350" windowHeight="19740" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="480" yWindow="480" windowWidth="37350" windowHeight="19740" firstSheet="1" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -408,11 +408,11 @@
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_FracNVolatilised_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_FracNVolatilised_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION ON SOURCE:";"Added 'NIR definition' column with MMS names that match NIR definitions."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_LivestockClasses">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Domestic";"Export mid fed";"Export long fed"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 11, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Treatment stage T","MMS m","NSW","ACT","QLD","NT","SA","VIC","WA","TAS","NIR definition";"Primary","Dry lot (Feedpad)",0.01,0.01,0.03,"No data",0.01,0.01,0.01,"No data","Drylot (feed pad)";"Secondary","Solid Storage (Stockpile)",0.02,0.02,0.02,"No data",0.02,0.02,0.02,"No data","Solid storage";"Secondary","Composting (Passive Windrow)",0.01,0.01,0.01,"No data",0.01,0.01,0.01,"No data","Composting (passive windrow)";"Secondary","Direct Application to soil",0,0,0,"No data",0,0,0,"No data","Direct application";"Tertiary","Uncovered anaerobic lagoon (Effluent pond)",0.75,0.75,0.77,"No data",0.75,0.75,0.77,"No data","Anaerobic lagoon"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 11, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Treatment stage T","MMS m","NSW","ACT","QLD","NT","SA","VIC","WA","TAS","NIR definition";"Primary","Dry lot (Feedpad)",0.01,0.01,0.03,0.03,0.01,0.01,0.01,0.01,"Drylot (feed pad)";"Secondary","Solid Storage (Stockpile)",0.02,0.02,0.02,0.02,0.02,0.02,0.02,0.02,"Solid storage";"Secondary","Composting (Passive Windrow)",0.01,0.01,0.01,0.01,0.01,0.01,0.01,0.01,"Composting (passive windrow)";"Secondary","Direct Application to soil",0,0,0,0,0,0,0,0,"Direct application";"Tertiary","Uncovered anaerobic lagoon (Effluent pond)",0.75,0.75,0.77,0.77,0.75,0.75,0.77,0.75,"Anaerobic lagoon"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.1.4: Beef feedlot cattle - MCFs (fraction) (MCFimT)")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Title">_xlfn.LAMBDA("Feedlot - MCFs")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Unit">_xlfn.LAMBDA("")</definedName>
-    <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION ON SOURCE:";"Duplicated NSW values for ACT";"Added NT and TAS columns with 'no data' values";"Added 'NIR definition' column with MMS names that match NIR definitions."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_Feedlot.SourceData_Feedlot_MCF_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION ON SOURCE:";"Duplicated NSW values for ACT";"Added NT column that duplicates QLD values as per advice from source data provider.";"Added TAS column that duplicates VIC values as per advice from source data provider.";"Added 'NIR definition' column with MMS names that match NIR definitions."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_MethaneEmissionsPotential_Data">_xlfn.LAMBDA(0.19)</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_MethaneEmissionsPotential_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.2.3 CONSTANTS")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_MethaneEmissionsPotential_Title">_xlfn.LAMBDA("Methane emissions potential.")</definedName>
@@ -501,7 +501,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="184">
   <si>
     <t>Home</t>
   </si>
@@ -993,12 +993,6 @@
   </si>
   <si>
     <t>EFPRP</t>
-  </si>
-  <si>
-    <t>apply queensland</t>
-  </si>
-  <si>
-    <t>use vic</t>
   </si>
   <si>
     <t>Month</t>
@@ -1607,7 +1601,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1687,12 +1681,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89996032593768116"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2134,10 +2122,10 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="15" borderId="2">
+    <xf numFmtId="0" fontId="57" fillId="14" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="16" borderId="2">
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="4" borderId="2">
@@ -2147,7 +2135,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2430,13 +2418,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="8" applyFont="1" applyFill="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="15" borderId="2" xfId="64">
+    <xf numFmtId="0" fontId="57" fillId="14" borderId="2" xfId="64">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="16" borderId="2" xfId="65">
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="2" xfId="65">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="4" borderId="2" xfId="66">
@@ -2539,6 +2524,126 @@
     <cellStyle name="Variable type other" xfId="65" xr:uid="{5D88A237-9D54-45E0-A48E-F67D0639FDE2}"/>
   </cellStyles>
   <dxfs count="75">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3834,126 +3939,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5334,8 +5319,8 @@
       <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3209853" cy="194990"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -5570,7 +5555,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -5635,8 +5620,8 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2256130" cy="332079"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -5876,7 +5861,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -6031,22 +6016,22 @@
     <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6162,49 +6147,49 @@
     <tableColumn id="1" xr3:uid="{25162FA7-7F7F-4C9C-8231-8FC51C581FD1}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6222,7 +6207,7 @@
     <tableColumn id="1" xr3:uid="{2BBE1D44-5D3C-421E-B886-5F058BD82B23}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6326,7 +6311,7 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="52" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="57" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6342,7 +6327,7 @@
     <tableColumn id="1" xr3:uid="{ACC4E2B3-A6FC-4D50-BE90-6D711BFC3B97}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="23">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6390,7 +6375,7 @@
     <tableColumn id="1" xr3:uid="{6328C683-420D-4EA6-AF9D-245995DC8FD1}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6408,7 +6393,7 @@
     <tableColumn id="1" xr3:uid="{FB787692-FEAA-422C-9A68-A116E1C1D839}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6426,7 +6411,7 @@
     <tableColumn id="1" xr3:uid="{E0DBFFCC-335E-4C29-BC47-5C2A3243CFF0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6458,49 +6443,49 @@
     <tableColumn id="1" xr3:uid="{8C0CBC0D-B831-4C7E-9F24-0EE0037F3E6B}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6545,22 +6530,22 @@
     <tableColumn id="1" xr3:uid="{FDCB848C-205F-48EA-BACF-F54BCD324E05}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6583,22 +6568,22 @@
     <tableColumn id="1" xr3:uid="{96F6B4E3-E1EE-445F-9BCE-628B89FC3727}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6616,7 +6601,7 @@
     <tableColumn id="1" xr3:uid="{9D472457-4D8B-44ED-9567-B889D058C2F1}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6636,13 +6621,13 @@
     <tableColumn id="1" xr3:uid="{C80C08D8-3F48-4E18-98E3-9B53ACB6C6D9}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6651,7 +6636,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="40" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D112:G117" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6925,7 +6910,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="894" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="503" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -6977,7 +6962,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7374,141 +7359,141 @@
       <c r="A1" s="63" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="110" t="s">
-        <v>183</v>
-      </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
-      <c r="AF1" s="111"/>
-      <c r="AG1" s="111"/>
+      <c r="C1" s="109" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
+      <c r="AC1" s="110"/>
+      <c r="AD1" s="110"/>
+      <c r="AE1" s="110"/>
+      <c r="AF1" s="110"/>
+      <c r="AG1" s="110"/>
     </row>
     <row r="2" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="111"/>
-      <c r="Y2" s="111"/>
-      <c r="Z2" s="111"/>
-      <c r="AA2" s="111"/>
-      <c r="AB2" s="111"/>
-      <c r="AC2" s="111"/>
-      <c r="AD2" s="111"/>
-      <c r="AE2" s="111"/>
-      <c r="AF2" s="111"/>
-      <c r="AG2" s="111"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="110"/>
+      <c r="AC2" s="110"/>
+      <c r="AD2" s="110"/>
+      <c r="AE2" s="110"/>
+      <c r="AF2" s="110"/>
+      <c r="AG2" s="110"/>
     </row>
     <row r="3" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112"/>
-      <c r="S3" s="112"/>
-      <c r="T3" s="112"/>
-      <c r="U3" s="112"/>
-      <c r="V3" s="112"/>
-      <c r="W3" s="112"/>
-      <c r="X3" s="112"/>
-      <c r="Y3" s="112"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="112"/>
-      <c r="AB3" s="112"/>
-      <c r="AC3" s="112"/>
-      <c r="AD3" s="112"/>
-      <c r="AE3" s="112"/>
-      <c r="AF3" s="112"/>
-      <c r="AG3" s="112"/>
-      <c r="AH3" s="112"/>
-      <c r="AI3" s="112"/>
-      <c r="AJ3" s="112"/>
-      <c r="AK3" s="112"/>
-      <c r="AL3" s="112"/>
-      <c r="AM3" s="112"/>
-      <c r="AN3" s="112"/>
-      <c r="AO3" s="112"/>
-      <c r="AP3" s="112"/>
-      <c r="AQ3" s="112"/>
-      <c r="AR3" s="112"/>
-      <c r="AS3" s="112"/>
-      <c r="AT3" s="112"/>
-      <c r="AU3" s="112"/>
-      <c r="AV3" s="112"/>
-      <c r="AW3" s="112"/>
-      <c r="AX3" s="112"/>
-      <c r="AY3" s="112"/>
-      <c r="AZ3" s="112"/>
-      <c r="BA3" s="112"/>
-      <c r="BB3" s="112"/>
-      <c r="BC3" s="112"/>
-      <c r="BD3" s="112"/>
-      <c r="BE3" s="112"/>
-      <c r="BF3" s="112"/>
-      <c r="BG3" s="112"/>
-      <c r="BH3" s="112"/>
-      <c r="BI3" s="112"/>
-      <c r="BJ3" s="112"/>
-      <c r="BK3" s="112"/>
-      <c r="BL3" s="112"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111"/>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111"/>
+      <c r="AA3" s="111"/>
+      <c r="AB3" s="111"/>
+      <c r="AC3" s="111"/>
+      <c r="AD3" s="111"/>
+      <c r="AE3" s="111"/>
+      <c r="AF3" s="111"/>
+      <c r="AG3" s="111"/>
+      <c r="AH3" s="111"/>
+      <c r="AI3" s="111"/>
+      <c r="AJ3" s="111"/>
+      <c r="AK3" s="111"/>
+      <c r="AL3" s="111"/>
+      <c r="AM3" s="111"/>
+      <c r="AN3" s="111"/>
+      <c r="AO3" s="111"/>
+      <c r="AP3" s="111"/>
+      <c r="AQ3" s="111"/>
+      <c r="AR3" s="111"/>
+      <c r="AS3" s="111"/>
+      <c r="AT3" s="111"/>
+      <c r="AU3" s="111"/>
+      <c r="AV3" s="111"/>
+      <c r="AW3" s="111"/>
+      <c r="AX3" s="111"/>
+      <c r="AY3" s="111"/>
+      <c r="AZ3" s="111"/>
+      <c r="BA3" s="111"/>
+      <c r="BB3" s="111"/>
+      <c r="BC3" s="111"/>
+      <c r="BD3" s="111"/>
+      <c r="BE3" s="111"/>
+      <c r="BF3" s="111"/>
+      <c r="BG3" s="111"/>
+      <c r="BH3" s="111"/>
+      <c r="BI3" s="111"/>
+      <c r="BJ3" s="111"/>
+      <c r="BK3" s="111"/>
+      <c r="BL3" s="111"/>
     </row>
     <row r="4" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="101" t="str">
@@ -7584,13 +7569,13 @@
         <v>Results</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
+      <c r="D5" s="112" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
       <c r="I5" s="96"/>
       <c r="J5" s="79"/>
       <c r="K5" s="79"/>
@@ -7651,13 +7636,13 @@
     <row r="6" spans="1:64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="114" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
+      <c r="D6" s="113" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
       <c r="I6" s="81"/>
       <c r="J6" s="78"/>
       <c r="K6" s="78"/>
@@ -12651,7 +12636,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="102" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12715,19 +12700,19 @@
         <v>117</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F6" s="100" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G6" s="100" t="s">
         <v>132</v>
       </c>
       <c r="H6" s="100" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="100" t="s">
         <v>145</v>
-      </c>
-      <c r="I6" s="100" t="s">
-        <v>147</v>
       </c>
       <c r="J6" s="100" t="s">
         <v>133</v>
@@ -12741,7 +12726,7 @@
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E7" s="98">
         <f>'3.1.1.1-2 Enteric Methane'!E67</f>
@@ -12764,7 +12749,7 @@
         <v>991.7664400000001</v>
       </c>
       <c r="J7" s="52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
@@ -12790,7 +12775,7 @@
         <v>991.7664400000001</v>
       </c>
       <c r="J8" s="93" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
@@ -14799,7 +14784,7 @@
         <v>250</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -14868,7 +14853,7 @@
         <v>Constants - Feedlot</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E15" s="50" cm="1">
         <f t="array" ref="E15">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$13) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$15), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14883,7 +14868,7 @@
         <v>5.5</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -14895,7 +14880,7 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E16" s="50" cm="1">
         <f t="array" ref="E16">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$13) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$16), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14910,7 +14895,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -14965,7 +14950,7 @@
     </row>
     <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E20" s="61" cm="1">
         <f t="array" ref="E20">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$18) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$20), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14980,7 +14965,7 @@
         <v>5.5</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -14989,7 +14974,7 @@
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="D21" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E21" s="61" cm="1">
         <f t="array" ref="E21">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$18) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$21), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -15004,7 +14989,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -15349,22 +15334,22 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="106" t="str" cm="1">
+      <c r="D13" s="105" t="str" cm="1">
         <f t="array" ref="D13:E15">_xlfn.CHOOSECOLS(EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction_Arguments(),1,2)</f>
         <v>I_j</v>
       </c>
-      <c r="E13" s="109" t="str">
+      <c r="E13" s="108" t="str">
         <v>dry matter intake</v>
       </c>
-      <c r="F13" s="108"/>
-      <c r="G13" s="106" t="str" cm="1">
+      <c r="F13" s="107"/>
+      <c r="G13" s="105" t="str" cm="1">
         <f t="array" ref="G13:H15">_xlfn.CHOOSECOLS(EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction_Arguments(),3,4)</f>
         <v>kg DM/head/day</v>
       </c>
-      <c r="H13" s="104" t="str">
+      <c r="H13" s="103" t="str">
         <v>Input</v>
       </c>
-      <c r="I13" s="107" t="str" cm="1">
+      <c r="I13" s="106" t="str" cm="1">
         <f t="array" aca="1" ref="I13" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$17),$D$17)</f>
         <v>M1_Table_I_j</v>
       </c>
@@ -15373,20 +15358,20 @@
       <c r="A14" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="106" t="str">
+      <c r="D14" s="105" t="str">
         <v>EE_j</v>
       </c>
-      <c r="E14" s="109" t="str">
+      <c r="E14" s="108" t="str">
         <v>ether extract as a percentage of I_j</v>
       </c>
-      <c r="F14" s="108"/>
-      <c r="G14" s="106" t="str">
+      <c r="F14" s="107"/>
+      <c r="G14" s="105" t="str">
         <v>per cent</v>
       </c>
-      <c r="H14" s="104" t="str">
+      <c r="H14" s="103" t="str">
         <v>Input</v>
       </c>
-      <c r="I14" s="107" t="str" cm="1">
+      <c r="I14" s="106" t="str" cm="1">
         <f t="array" aca="1" ref="I14" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$22),$D$22)</f>
         <v>M1_Table_EE_j</v>
       </c>
@@ -15396,20 +15381,20 @@
         <f>HYPERLINK("#'Constants - Feedlot'!A1", "Constants - Feedlot")</f>
         <v>Constants - Feedlot</v>
       </c>
-      <c r="D15" s="106" t="str">
+      <c r="D15" s="105" t="str">
         <v>NDF_j</v>
       </c>
-      <c r="E15" s="109" t="str">
+      <c r="E15" s="108" t="str">
         <v>neutral detergent fibre as a percentage of I_j</v>
       </c>
-      <c r="F15" s="108"/>
-      <c r="G15" s="106" t="str">
+      <c r="F15" s="107"/>
+      <c r="G15" s="105" t="str">
         <v>per cent</v>
       </c>
-      <c r="H15" s="104" t="str">
+      <c r="H15" s="103" t="str">
         <v>Input</v>
       </c>
-      <c r="I15" s="107" t="str" cm="1">
+      <c r="I15" s="106" t="str" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$27),$D$27)</f>
         <v>M1_Table_NDF_j</v>
       </c>
@@ -15503,18 +15488,18 @@
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="86" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M22" s="86" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="85" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M23" s="85" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15575,18 +15560,18 @@
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="86" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M27" s="86" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="85" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15646,18 +15631,18 @@
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="86" t="s">
+        <v>171</v>
+      </c>
+      <c r="M32" s="86" t="s">
         <v>173</v>
-      </c>
-      <c r="M32" s="86" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="33" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="M33" s="85" t="s">
         <v>174</v>
-      </c>
-      <c r="M33" s="85" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="34" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15779,60 +15764,60 @@
     </row>
     <row r="47" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="106" t="str" cm="1">
+      <c r="D48" s="105" t="str" cm="1">
         <f t="array" ref="D48:E50">_xlfn.CHOOSECOLS(EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments(),1,2)</f>
         <v>D_j</v>
       </c>
-      <c r="E48" s="109" t="str">
+      <c r="E48" s="108" t="str">
         <v>duration of stay of each cattle lot</v>
       </c>
-      <c r="F48" s="108"/>
-      <c r="G48" s="106" t="str" cm="1">
+      <c r="F48" s="107"/>
+      <c r="G48" s="105" t="str" cm="1">
         <f t="array" ref="G48:H50">_xlfn.CHOOSECOLS(EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments(),3,4)</f>
         <v>days</v>
       </c>
-      <c r="H48" s="104" t="str">
+      <c r="H48" s="103" t="str">
         <v>Input</v>
       </c>
-      <c r="I48" s="107" t="str" cm="1">
+      <c r="I48" s="106" t="str" cm="1">
         <f t="array" aca="1" ref="I48" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$52),$D$52)</f>
         <v>Table_D_j</v>
       </c>
     </row>
     <row r="49" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="106" t="str">
+      <c r="D49" s="105" t="str">
         <v>M_j</v>
       </c>
-      <c r="E49" s="109" t="str">
+      <c r="E49" s="108" t="str">
         <v>daily methane production</v>
       </c>
-      <c r="F49" s="108"/>
-      <c r="G49" s="106" t="str">
+      <c r="F49" s="107"/>
+      <c r="G49" s="105" t="str">
         <v>kg CH4/head/day</v>
       </c>
-      <c r="H49" s="105" t="str">
+      <c r="H49" s="104" t="str">
         <v>Calculated from 3.1.1.1, (2)</v>
       </c>
-      <c r="I49" s="107" t="str" cm="1">
+      <c r="I49" s="106" t="str" cm="1">
         <f t="array" aca="1" ref="I49" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$32),$D$32)</f>
         <v>M1_Table_M_j</v>
       </c>
     </row>
     <row r="50" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="106" t="str">
+      <c r="D50" s="105" t="str">
         <v>N_j</v>
       </c>
-      <c r="E50" s="109" t="str">
+      <c r="E50" s="108" t="str">
         <v>numbers of feedlot cattle in each cattle lot</v>
       </c>
-      <c r="F50" s="108"/>
-      <c r="G50" s="106" t="str">
+      <c r="F50" s="107"/>
+      <c r="G50" s="105" t="str">
         <v>head</v>
       </c>
-      <c r="H50" s="104" t="str">
+      <c r="H50" s="103" t="str">
         <v>Input</v>
       </c>
-      <c r="I50" s="107" t="str" cm="1">
+      <c r="I50" s="106" t="str" cm="1">
         <f t="array" aca="1" ref="I50" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$57),$D$57)</f>
         <v>Table_N_j</v>
       </c>
@@ -15991,7 +15976,7 @@
     <row r="66" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="89" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E67" s="90">
         <f>SUM(D65:F65)</f>
@@ -16002,7 +15987,7 @@
         <v>t CH4</v>
       </c>
       <c r="M67" s="89" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N67" s="90">
         <f>SUM(M65:O65)</f>
@@ -17443,13 +17428,13 @@
     </row>
     <row r="85" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="53" t="str">
-        <v>Added NT and TAS columns with 'no data' values</v>
+        <v>Added NT column that duplicates QLD values as per advice from source data provider.</v>
       </c>
       <c r="M85" s="1"/>
     </row>
     <row r="86" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="53" t="str">
-        <v>Added 'NIR definition' column with MMS names that match NIR definitions.</v>
+        <v>Added TAS column that duplicates VIC values as per advice from source data provider.</v>
       </c>
       <c r="M86" s="1"/>
     </row>
@@ -17512,9 +17497,9 @@
         <f t="array" ref="H89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.03</v>
       </c>
-      <c r="I89" s="103" t="str" cm="1">
+      <c r="I89" s="37" cm="1">
         <f t="array" ref="I89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.03</v>
       </c>
       <c r="J89" s="37" cm="1">
         <f t="array" ref="J89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17528,9 +17513,9 @@
         <f t="array" ref="L89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.01</v>
       </c>
-      <c r="M89" s="103" t="str" cm="1">
+      <c r="M89" s="37" cm="1">
         <f t="array" ref="M89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.01</v>
       </c>
       <c r="N89" s="37" t="str" cm="1">
         <f t="array" ref="N89">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17558,9 +17543,9 @@
         <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.02</v>
       </c>
-      <c r="I90" s="103" t="str" cm="1">
+      <c r="I90" s="37" cm="1">
         <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.02</v>
       </c>
       <c r="J90" s="37" cm="1">
         <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17574,9 +17559,9 @@
         <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.02</v>
       </c>
-      <c r="M90" s="103" t="str" cm="1">
+      <c r="M90" s="37" cm="1">
         <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.02</v>
       </c>
       <c r="N90" s="37" t="str" cm="1">
         <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17604,9 +17589,9 @@
         <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.01</v>
       </c>
-      <c r="I91" s="103" t="str" cm="1">
+      <c r="I91" s="37" cm="1">
         <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.01</v>
       </c>
       <c r="J91" s="37" cm="1">
         <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17620,9 +17605,9 @@
         <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.01</v>
       </c>
-      <c r="M91" s="103" t="str" cm="1">
+      <c r="M91" s="37" cm="1">
         <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.01</v>
       </c>
       <c r="N91" s="37" t="str" cm="1">
         <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17650,9 +17635,9 @@
         <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0</v>
       </c>
-      <c r="I92" s="103" t="str" cm="1">
+      <c r="I92" s="37" cm="1">
         <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0</v>
       </c>
       <c r="J92" s="37" cm="1">
         <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17666,9 +17651,9 @@
         <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0</v>
       </c>
-      <c r="M92" s="103" t="str" cm="1">
+      <c r="M92" s="37" cm="1">
         <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0</v>
       </c>
       <c r="N92" s="37" t="str" cm="1">
         <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17696,9 +17681,9 @@
         <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.77</v>
       </c>
-      <c r="I93" s="103" t="str" cm="1">
+      <c r="I93" s="37" cm="1">
         <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.77</v>
       </c>
       <c r="J93" s="37" cm="1">
         <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17712,9 +17697,9 @@
         <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
         <v>0.77</v>
       </c>
-      <c r="M93" s="103" t="str" cm="1">
+      <c r="M93" s="37" cm="1">
         <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
-        <v>No data</v>
+        <v>0.75</v>
       </c>
       <c r="N93" s="37" t="str" cm="1">
         <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</f>
@@ -17722,12 +17707,7 @@
       </c>
     </row>
     <row r="94" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I94" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M94" s="24" t="s">
-        <v>139</v>
-      </c>
+      <c r="M94" s="24"/>
     </row>
     <row r="95" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M95" s="24"/>
@@ -21014,10 +20994,10 @@
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D212" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E212" s="37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
@@ -21163,49 +21143,49 @@
         <v>42</v>
       </c>
       <c r="E231" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F231" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="G231" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="F231" s="36" t="s">
+      <c r="H231" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="G231" s="37" t="s">
+      <c r="I231" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H231" s="37" t="s">
+      <c r="J231" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="I231" s="37" t="s">
+      <c r="K231" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="J231" s="37" t="s">
+      <c r="L231" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="K231" s="37" t="s">
+      <c r="M231" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="L231" s="37" t="s">
+      <c r="N231" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="M231" s="37" t="s">
+      <c r="O231" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="N231" s="37" t="s">
+      <c r="P231" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="O231" s="37" t="s">
+      <c r="Q231" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="R231" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="P231" s="37" t="s">
+      <c r="S231" s="37" t="s">
         <v>162</v>
-      </c>
-      <c r="Q231" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="R231" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="S231" s="37" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
@@ -22964,12 +22944,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23168,24 +23150,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMATABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA1ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AFwAbgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA2ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA5ACkAOwBcAG4AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAE0ATQBTAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABtAGkAZAAgAGYAZQBkAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbABvAG4AZwAgAGYAZQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATABlAG4AZwB0AGgAIABvAGYAIABTAHQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAMQAtADgAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAOAAxAC0AMgAwADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIAMgAwADEAKwAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBhAG0AZQBkACAAJwBjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAJwAgAGMAbwBsAHUAbQBuACAALQAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAYQBzACAAaABlAGEAZABlAHIAIAAnAFUAbgBpAHQAJwAgAHcAaABpAGMAaAAgAGMAbwB2AGUAcgBzACAAdAB3AG8AIABjAG8AbAB1AG0AbgBzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAANwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAANwAwACwAIAA3ADAALAAgADcAMAAsACAANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADAALgAwACwAIAAxADAALgAwACwAIAAxADAALgA0ACwAIAAxADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAyADEALgAxACwAIAAyADAALgA0ACwAIAAyADAALgA0ACwAIAAyADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADEAMQA1ACwAIAAxADEANQAsACAAMQAyADAALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAxAC4AMgAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADEAMgAuADUALAAgADEAMgAuADcALAAgADEAMgAuADcALAAgADEAMgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAOQAuADAALAAgADgALgA1ACwAIAA4AC4AMgAsACAAOAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADYALgA2ACwAIAA3AC4AMAAsACAANwAuADAALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgAgAGMAbwBsAHUAbQBuACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AGUAZAAgAE4ARABGACAAYQBuAGQAIABFAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAdgBhAGwAdQBlAHMAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAA4ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgAzAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA0AC4ANQAsACAANAAuADUALAAgADQALgA4ACwAIAA0AC4AOAAsACAAMAAuADAANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAwAC4AMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADUALAAgADUALgA1ACwAIAAwAC4AMAA1ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABhAG4AZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AcwAgAHcAaQB0AGgAIAAnAG4AbwAgAGQAYQB0AGEAJwAgAHYAYQBsAHUAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACkAXAAiACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA3ACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFQAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMAA1ADQALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAUABvAG4AZAApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVAAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADYALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMgA1ACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgA0ACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACkAXAAiACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBfAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ARABfAGoAIAA9ACAAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXABuAE0AXwBqAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAF8AagAsACAATQBfAGoAbQBUACwAIABOAF8AagAsAFwAbgAgACAAIAAgACgARABfAGoAIAAqACAATQBfAGoAbQBUACAAKgAgAE4AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAXAAiAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAbQBUAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMQAgACgAMgApACgAMwApACgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBfAGoAbQA1AFQAMQBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0ANQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0ANQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQA1AFQAMQAsACAATQBDAEYAXwBpAG0ANQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABNAEMARgBfAGkAbQA1ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAEMARgBfAGkAbQA1ACkALAAgAE0AQwBGAF8AaQBtADUALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0ANQBUADEAIAAqACAATQBDAEYAXwBpAG0ANQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQA1AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0ANQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMQAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0ANQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQA1AFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBNAF8AagBtAFQAMgBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBMACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBMACwAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQBUADIALAAgAE0AQwBGAF8AaQBtACwAIAByAGgAbwAsAFwAbgAgACAAIAAgACgAMQAgAC0AIABWAFMATAApACAAKgAgAFYAUwBfAGoAIAAqACAAQgBPACAAKgAgAE0ATQBTAF8AbQBUADIAIAAqACAATQBDAEYAXwBpAG0AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAFQAPQAyAH0APQAoADEALQBWAFMATAApAFwAXAB0AGkAbQBlAHMAIABWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMATABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABlACAAYQBuAGQAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAGEAbgBkACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIATQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAbgBNAF8AagBtADEAVAAzAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADEALABUAD0AMwB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQAxAFQAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtADEAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQAxAFQAMwAsACAATQBDAEYAXwBpAG0AMQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AMQBUADMAIAAqACAATQBDAEYAXwBpAG0AMQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMQAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AMQBUADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADEAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAZQAgAGEAbgBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQAxAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBNAGUAYQBuACAAYQBuAG4AdQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AVgBTAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBEAE0ARABfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBBACkAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEEAIAA9ACAAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALAAgAEQATQBEAF8AagAsACAAQQAsAFwAbgAgACAAIAAgAEkAXwBqACAAKgAgACgAMQAgAC0AIABEAE0ARABfAGoAKQAgACoAIAAoADEAIAAtACAAQQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAXAAiACwAXAAiAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AOQAgAE0AYQBuAHUAcgBlACAAQQBwAHAAbABpAGUAZAAgAHQAbwAgAFMAbwBpAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXABuAE0ATgBfAGoAbQBUADIAMwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAMwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAzACwAIABFAEYAXwBtAFQAMgAzACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAMwAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAMwAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACkAKQAgACoAIABQAEYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMQB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAgAFAARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgAzAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACwAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA2ACkAKAA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAyADMAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5AFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAzAFwAbgBrAGcAIABOAFwAbgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AUABGACkAXABuAE0ATgBfAGoAbQBUADIAMwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AbQBUADIAMwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AUABGACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQAMgAzACwAIABFAEYAXwBtAFQAMgAzACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACwAIABQAEYALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQBUADIAMwAgACoAIAAoADEAIAAtACAARQBGAF8AbQBUADIAMwAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAMgAzACkAKQAgACoAIAAoADEAIAAtACAAUABGACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AcwBjAG8AcABlADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AOQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAF8AewBzAGMAbwBwAGUAMwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAD0AMgAsADMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEUARgBfAHsAbQBUAD0AMgAsADMAfQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAD0AMgAsADMAfQApACkAXABcAHQAaQBtAGUAcwAoADEALQBQAEYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMgAzAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAYQBuAGQAIAB0AGUAcgB0AGkAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAcwB0AGEAZwBlAHMAIABhAHMAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACwAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA2ACkAKAA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AVAAyADMAXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTAFwAIgAsAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYQBuAGkAbQBhAGwAIAB3AGEAcwB0AGUAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABmAGUAZQBkAGwAbwB0ACAAYgBvAHUAbgBkAGEAcgB5AFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgA1ACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAAQQB0AG0AbwBzAHAAaABlAHIAaQBjACAARABlAHAAbwBzAGkAdABpAG8AbgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAF8ATgAyAE8AYQBkAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAYQBkAH0APQAoAE0ATQBTAF8AewBBAFQATQBPAFMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBNAE0AUwBfAEEAVABNAE8AUwAgAD0AIABtAGEAcwBzACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABNAE0AUwAgADoAIABrAGcAIABOAFwAbgBFAEYAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAcgBhAHQAaQBvAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBNAFMAXwBBAFQATQBPAFMALAAgAEUARgBfAE4AMgBPACwAIABDAF8ATgAyAE8ALABcAG4AIAAgACAAIAAoAE0ATQBTAF8AQQBUAE0ATwBTACAAKgAgAEUARgBfAE4AMgBPACAAKgAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBhAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4ANQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGEAZAB9AD0AKABNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAEEAVABNAE8AUwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADUAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8ATgAyAE8AXAAiACwAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAXAAiACwAIABcACIAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAIABuAGkAdAByAG8AZwBlAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBNAE0AUwBfAEEAVABNAE8AUwBcAG4AawBnACAATgBcAG4ATQBNAFMAXwB7AEEAVABNAE8AUwB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABNAE4AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMARwBBAFMATQBfAHsAbQBUAH0AKQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBfAG0AVAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAaQBuACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEYAcgBhAGMARwBBAFMATQBfAG0AVAAsAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACAAKgAgAEYAcgBhAGMARwBBAFMATQBfAG0AVABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAEEAVABNAE8AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAATQBNAFMAIAAoAGUAeABjAGwAdQBkAGkAbgBnACAATQBOAF8AaQBqAG0AMQAzAFQAMgApAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAyACkAKAA2ACkAKAA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVABcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwBcACIALAAgAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4AMwAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEQAaQByAGUAYwB0ACAATgAyAE8AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AcwBcAG4ARQBfAE4AMgBPAGQAaQByAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPACwAZABpAHIAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoAbQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBNAE4AXwBqAG0AVAAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAATgBcAG4ARQBGAF8AagBtACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4AQwBfAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAcgBhAHQAaQBvAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtAFQALAAgAEUARgBfAGoAbQAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPACwAZABpAHIAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGoAbQB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADMAIAAoADIAKQAoADYAKQAoADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBtAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTAFwAIgAsAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBfAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsAFwAIgByAGEAdABpAG8AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBOAF8AagBtADUAVAAxAFwAbgBrAGcAIABOAFwAbgBNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAG4AQQBFAF8AagAgAD0AIAB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAawBnACAATgBcAG4ATQBNAFMAXwBqAG0ANQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUAXwBqACwAIABNAE0AUwBfAGoAbQA1AFQAMQAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAATQBNAFMAXwBqAG0ANQBUADEAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEUAXwBqAFwAIgAsAFwAIgB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADMAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBqAG0ANQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcAG4AQQBFAF8AagBcAG4AawBnACAATgBcAG4AQQBFAF8AewBqAH0APQBOAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE4ARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAH0AXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGgAZQBhAGQAXABuAE4ARQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGQAYQB5AHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAsACAATgBFAF8AagAsACAARABfAGoALABcAG4AIAAgACAAIABOAF8AagAgACoAIABOAEUAXwBqACAAKgAgAEQAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBuAG4AdQBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAGYAcgBvAG0AIABlAGEAYwBoACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBFAF8AagBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADMAIAAoADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXABuAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAcABlAHIAIABoAGUAYQBkACAAcABlAHIAIABkAGEAeQBcAG4ATgBFAF8AagBcAG4AawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBFAF8AewBqAH0APQBOAEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAE4AUgBfAHsAagB9ACkAXABuAE4ASQBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIAA6ACAAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBSAF8AagAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgB0AGEAawBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBJAF8AagAsACAATgBSAF8AagAsAFwAbgAgACAAIAAgAE4ASQBfAGoAIAAqACAAKAAxACAALQAgAE4AUgBfAGoAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABwAGUAcgAgAGgAZQBhAGQAIABwAGUAcgAgAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXwB7AGoAfQA9AE4ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ATgBSAF8AewBqAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ASQBfAGoAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUgBfAGoAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHIAZQB0AGUAbgB0AGkAbwBuACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQBcAG4ATgBJAF8AagBcAG4AawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEMAUABfAGoAIAA9ACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ANgAuADIANQAgAD0AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdgBlAHIAdABpAG4AZwAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABpAG4AdABvACAAbgBpAHQAcgBvAGcAZQBuACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABDAFAAXwBqACwAXABuACAAIAAgACAASQBfAGoAIAAqACAAQwBQAF8AagAgAC8AIAA2AC4AMgA1AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBJAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEMAUABfAHsAagB9AFwAXABkAGkAdgAgADYALgAyADUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAFAAXwBqAFwAIgAsAFwAIgBjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIANgAuADIANQBcACIALABcACIAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHYAZQByAHQAaQBuAGcAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAaQBuAHQAbwAgAG4AaQB0AHIAbwBnAGUAbgBcACIALAAgAFwAIgByAGEAdABpAG8AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBOAF8AagBtAFQAMgBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAG4ATgBUAF8AagBtAFQAMgAgAD0AIABuAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIABzAGUAYwBvAG4AZABhAHIAeQAgAHQAcgBlAGEAdABtAGUAbgB0ACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ATQBNAFMAXwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIALAAgAE0ATQBTAF8AagBtAFQAMgAsAFwAbgAgACAAIAAgAE4AVABfAGoAbQBUADIAIAAqACAATQBNAFMAXwBqAG0AVAAyAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AewBqAG0ALABUAD0AMgB9AD0ATgBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAF8AagBtAFQAMgBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBcAG4ATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE4AVABfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE4AVABfAHsAagBtACwAVAA9ADIAfQA9ACgATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQA9ADUAfQAtAEUARgBfAHsAbQA9ADUAfQApACkALQBNAE4AXwB7AGoAbQAsAFQAPQAzAH0AXABuAE0ATgBfAGoAbQA1AFQAMQAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABNAE0AUwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtADUAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ARQBGAF8AbQA1ACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZABlAHAAbwBzAGkAdABlAGQAXABuAE0ATgBfAGoAbQBUADMAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIAA6ACAAawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAF8AagBtADUAVAAxACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtADUALAAgAEUARgBfAG0ANQAsACAATQBOAF8AagBtAFQAMwAsAFwAbgAgACAAIAAgACgATQBOAF8AagBtADUAVAAxACAAKgAgACgAMQAgAC0AIABGAHIAYQBjAEcAQQBTAE0AXwBtADUAIAAtACAARQBGAF8AbQA1ACkAKQAgAC0AIABNAE4AXwBqAG0AVAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAFQAXwBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AewBqAG0ALABUAD0AMgB9AD0AKABNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAD0ANQB9AC0ARQBGAF8AewBtAD0ANQB9ACkAKQAtAE0ATgBfAHsAagBtACwAVAA9ADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQA1AFQAMQBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADMAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAF8AbQA1AFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbQA1AFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGQAZQBwAG8AcwBpAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAMwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADMAIAAoADgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXABuAE0ATgBfAGoAbQAxAFQAMwBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0AMQAsAFQAPQAzAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADEAVAAzACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEUAXwBqACwAIABNAE0AUwBfAGoAbQAxAFQAMwAsAFwAbgAgACAAIAAgAEEARQBfAGoAIAAqACAATQBNAFMAXwBqAG0AMQBUADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwBqAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA4ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEUAXwBqAFwAIgAsAFwAIgB0AG8AdABhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABiAHkAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAawBnACAATgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADMAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBqAG0AMQBUADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAdABlAHIAdABpAGEAcgB5ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEYAZQBlAGQAbABvAHQAIABCAGUAZQBmAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgARABfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABOAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBEAF8AagAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGQAYQB5AHMAKQBcAG4ATQBfAGoAIAA9ACAAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdAAgACgAaABlAGEAZAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqACwAIABOAF8AagAsAFwAbgAgACAAIAAgACgARABfAGoAIAAqACAATQBfAGoAIAAqACAATgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABmAGUAZQBkAGwAbwB0ACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQAoADUALgAxADEAXABcAHQAaQBtAGUAcwAgAEkAXwBqAC0ANAAuADAAMABcAFwAdABpAG0AZQBzACAARQBFAF8AagArADIALgAyADYAXABcAHQAaQBtAGUAcwAgAE4ARABGAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBFAEUAXwBqACAAPQAgAGUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ATgBEAEYAXwBqACAAPQAgAG4AZQB1AHQAcgBhAGwAIABkAGUAdABlAHIAZwBlAG4AdAAgAGYAaQBiAHIAZQAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALAAgAEUARQBfAGoALAAgAE4ARABGAF8AagAsAFwAbgAgACAAIAAgACgANQAuADEAMQAgACoAIABJAF8AagAgAC0AIAA0AC4AMAAwACAAKgAgAEUARQBfAGoAIAArACAAMgAuADIANgAgACoAIABOAEQARgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbABtAGUAaQBkAGEAIABlAHQAIABhAGwALgAgACgAMgAwADIANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQAoADUALgAxADEAXABcAHQAaQBtAGUAcwAgAEkAXwBqAC0ANAAuADAAMABcAFwAdABpAG0AZQBzACAARQBFAF8AagArADIALgAyADYAXABcAHQAaQBtAGUAcwAgAE4ARABGAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsACAAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEUAXwBqAFwAIgAsACAAXAAiAGUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARABGAF8AagBcACIALAAgAFwAIgBuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMATABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA1ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AFwAbgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA2ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA5ACkAOwBcAG4AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAE0ATQBTAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABtAGkAZAAgAGYAZQBkAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbABvAG4AZwAgAGYAZQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATABlAG4AZwB0AGgAIABvAGYAIABTAHQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAMQAtADgAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAOAAxAC0AMgAwADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIAMgAwADEAKwAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBhAG0AZQBkACAAJwBjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAJwAgAGMAbwBsAHUAbQBuACAALQAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAYQBzACAAaABlAGEAZABlAHIAIAAnAFUAbgBpAHQAJwAgAHcAaABpAGMAaAAgAGMAbwB2AGUAcgBzACAAdAB3AG8AIABjAG8AbAB1AG0AbgBzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAANwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAANwAwACwAIAA3ADAALAAgADcAMAAsACAANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADAALgAwACwAIAAxADAALgAwACwAIAAxADAALgA0ACwAIAAxADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAyADEALgAxACwAIAAyADAALgA0ACwAIAAyADAALgA0ACwAIAAyADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADEAMQA1ACwAIAAxADEANQAsACAAMQAyADAALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAxAC4AMgAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADEAMgAuADUALAAgADEAMgAuADcALAAgADEAMgAuADcALAAgADEAMgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAOQAuADAALAAgADgALgA1ACwAIAA4AC4AMgAsACAAOAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADYALgA2ACwAIAA3AC4AMAAsACAANwAuADAALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgAgAGMAbwBsAHUAbQBuACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AGUAZAAgAE4ARABGACAAYQBuAGQAIABFAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAdgBhAGwAdQBlAHMAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAA4ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgAzAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA0AC4ANQAsACAANAAuADUALAAgADQALgA4ACwAIAA0AC4AOAAsACAAMAAuADAANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAwAC4AMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADUALAAgADUALgA1ACwAIAAwAC4AMAA1ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABjAG8AbAB1AG0AbgAgAHQAaABhAHQAIABkAHUAcABsAGkAYwBhAHQAZQBzACAAUQBMAEQAIAB2AGEAbAB1AGUAcwAgAGEAcwAgAHAAZQByACAAYQBkAHYAaQBjAGUAIABmAHIAbwBtACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAcAByAG8AdgBpAGQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AIAB0AGgAYQB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAgAFYASQBDACAAdgBhAGwAdQBlAHMAIABhAHMAIABwAGUAcgAgAGEAZAB2AGkAYwBlACAAZgByAG8AbQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHAAcgBvAHYAaQBkAGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBFAEYAbQBUACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADAANQA0ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADAAMAA1ACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgAwADEALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAFAAbwBuAGQAKQBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADYAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADYAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgA2ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4ANAAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADMANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAXwBqACAAPQAgAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgBNAF8AagBtAFQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqAG0AVAAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqAG0AVAAgACoAIABOAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsAFwAIgBsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADIAKQAoADMAKQAoADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0AXwBqAG0ANQBUADEAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQA1AH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtADUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0ANQBUADEALAAgAE0AQwBGAF8AaQBtADUALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBDAEYAXwBpAG0ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBDAEYAXwBpAG0ANQApACwAIABNAEMARgBfAGkAbQA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADUAVAAxACAAKgAgAE0AQwBGAF8AaQBtADUAIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQA1AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADUAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAZQAgAGEAbgBkACAAZAByAHkAbABvAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0ANQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBfAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMATAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAGEAbgBkACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMATAAsACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0AVAAyACwAIABNAEMARgBfAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIAAoADEAIAAtACAAVgBTAEwAKQAgACoAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AVAAyACAAKgAgAE0AQwBGAF8AaQBtACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAZQAgAGEAbgBkACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMQAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABhAG4AZAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAE0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcAG4ATQBfAGoAbQAxAFQAMwBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0AMQBUADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBfAGkAbQAxACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAGEAbgBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0AMQBUADMALAAgAE0AQwBGAF8AaQBtADEALAAgAHIAaABvACwAXABuACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADEAVAAzACAAKgAgAE0AQwBGAF8AaQBtADEAIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBtADEAVAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQAxAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAagBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQAxAFQAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AMQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIATQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAFMAXwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBBACAAPQAgAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABEAE0ARABfAGoALAAgAEEALABcAG4AIAAgACAAIABJAF8AagAgACoAIAAoADEAIAAtACAARABNAEQAXwBqACkAIAAqACAAKAAxACAALQAgAEEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAXwB7AGoAfQA9AEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAEEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0ARABfAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAFwAIgAsAFwAIgBhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADkAIABNAGEAbgB1AHIAZQAgAEEAcABwAGwAaQBlAGQAIAB0AG8AIABTAG8AaQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMQBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAxAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACAAUABGAFwAbgBNAE4AXwBqAG0AVAAyADMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyADMAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGYAZQBlAGQAbABvAHQAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIAMwAsACAARQBGAF8AbQBUADIAMwAsACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAsACAAUABGACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0AVAAyADMAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyADMAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwApACkAIAAqACAAUABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAMwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgAsAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANgApACgAOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAbgBNAE4AXwBqAG0AVAAyADMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyADMAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGYAZQBlAGQAbABvAHQAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIAMwAsACAARQBGAF8AbQBUADIAMwAsACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAsACAAUABGACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0AVAAyADMAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyADMAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwApACkAIAAqACAAKAAxACAALQAgAFAARgApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AUABGACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAMwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgAsAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANgApACgAOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBfAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGEAZAB9AD0AKABNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE0AUwBfAEEAVABNAE8AUwAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9ACgATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgA1ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ATQBNAFMAXwBBAFQATQBPAFMAXABuAGsAZwAgAE4AXABuAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAE0ATgBfAGkAagBtADEAMwBUADIAKQAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQALABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAgACoAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAG4AaQB0AHIAbwBnAGUAbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAHsAQQBUAE0ATwBTAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAE0ATgBfAGkAagBtADEAMwBUADIAKQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgAMgApACgANgApACgAOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADMAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABEAGkAcgBlAGMAdAAgAE4AMgBPACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAHMAXABuAEUAXwBOADIATwBkAGkAcgBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGQAaQByAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqAG0AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAGoAbQAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABNAE4AXwBqAG0AVAAsACAARQBGAF8AagBtACwAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AZABpAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGQAaQByAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqAG0AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAyACkAKAA2ACkAKAA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoAbQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALABcACIAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0ATgBfAGoAbQA1AFQAMQBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0ANQBUADEALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADUAVAAxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADUAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAZgByAG8AbQAgAGUAYQBjAGgAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXABuAEEARQBfAGoAXABuAGsAZwAgAE4AXABuAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAbgBOAEUAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAEQAXwBqACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4ARQBfAGoALAAgAEQAXwBqACwAXABuACAAIAAgACAATgBfAGoAIAAqACAATgBFAF8AagAgACoAIABEAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwB7AGoAfQA9AE4AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATgBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBfAGoAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgBOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAHAAZQByACAAaABlAGEAZAAgAHAAZQByACAAZABhAHkAXABuAE4ARQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ARQBfAHsAagB9AD0ATgBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBOAFIAXwB7AGoAfQApAFwAbgBOAEkAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AUgBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcgBlAHQAZQBuAHQAaQBvAG4AIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AdABhAGsAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4ASQBfAGoALAAgAE4AUgBfAGoALABcAG4AIAAgACAAIABOAEkAXwBqACAAKgAgACgAMQAgAC0AIABOAFIAXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAcABlAHIAIABoAGUAYQBkACAAcABlAHIAIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAF8AewBqAH0APQBOAEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAE4AUgBfAHsAagB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEkAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFIAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXABuAE4ASQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ASQBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABDAFAAXwB7AGoAfQBcAFwAZABpAHYAIAA2AC4AMgA1AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBDAFAAXwBqACAAPQAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuADYALgAyADUAIAA9ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHYAZQByAHQAaQBuAGcAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAaQBuAHQAbwAgAG4AaQB0AHIAbwBnAGUAbgAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAAQwBQAF8AagAsAFwAbgAgACAAIAAgAEkAXwBqACAAKgAgAEMAUABfAGoAIAAvACAANgAuADIANQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABDAFAAXwB7AGoAfQBcAFwAZABpAHYAIAA2AC4AMgA1AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBQAF8AagBcACIALABcACIAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADYALgAyADUAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB2AGUAcgB0AGkAbgBnACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGkAbgB0AG8AIABuAGkAdAByAG8AZwBlAG4AXAAiACwAIABcACIAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0ATgBfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABuAE4AVABfAGoAbQBUADIAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACwAIABNAE0AUwBfAGoAbQBUADIALABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACAAKgAgAE0ATQBTAF8AagBtAFQAMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABfAGoAbQBUADIAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXABuAE4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBOAFQAXwBqAG0AVAAyAFwAbgBrAGcAIABOAFwAbgBOAFQAXwB7AGoAbQAsAFQAPQAyAH0APQAoAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0APQA1AH0ALQBFAEYAXwB7AG0APQA1AH0AKQApAC0ATQBOAF8AewBqAG0ALABUAD0AMwB9AFwAbgBNAE4AXwBqAG0ANQBUADEAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQA1ACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEUARgBfAG0ANQAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGQAZQBwAG8AcwBpAHQAZQBkAFwAbgBNAE4AXwBqAG0AVAAzACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAAOgAgAGsAZwAgAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQA1AFQAMQAsACAARgByAGEAYwBHAEEAUwBNAF8AbQA1ACwAIABFAEYAXwBtADUALAAgAE0ATgBfAGoAbQBUADMALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQA1AFQAMQAgACoAIAAoADEAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQA1ACAALQAgAEUARgBfAG0ANQApACkAIAAtACAATQBOAF8AagBtAFQAMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AVABfAHsAagBtACwAVAA9ADIAfQA9ACgATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQA9ADUAfQAtAEUARgBfAHsAbQA9ADUAfQApACkALQBNAE4AXwB7AGoAbQAsAFQAPQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0ANQBUADEAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0ANQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0ANQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA4ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AMQBUADMAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABOAFwAbgBNAE0AUwBfAGoAbQAxAFQAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0AMQBUADMALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADEAVAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADEAVAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAOAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQAxACwAVAA9ADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAxADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABGAGUAZQBkAGwAbwB0ACAAQgBlAGUAZgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGYAZQBlAGQAbABvAHQAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0ACAAKABkAGEAeQBzACkAXABuAE0AXwBqACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGgAZQBhAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqACAAKgAgAE4AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABEAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAXABcAHQAaQBtAGUAcwAgAE4AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ASQBfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARQBFAF8AagAgAD0AIABlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAE4ARABGAF8AagAgAD0AIABuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABFAEUAXwBqACwAIABOAEQARgBfAGoALABcAG4AIAAgACAAIAAoADUALgAxADEAIAAqACAASQBfAGoAIAAtACAANAAuADAAMAAgACoAIABFAEUAXwBqACAAKwAgADIALgAyADYAIAAqACAATgBEAEYAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGwAbQBlAGkAZABhACAAZQB0ACAAYQBsAC4AIAAoADIAMAAyADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBFAF8AagBcACIALAAgAFwAIgBlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEQARgBfAGoAXAAiACwAIABcACIAbgBlAHUAdAByAGEAbAAgAGQAZQB0AGUAcgBnAGUAbgB0ACAAZgBpAGIAcgBlACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -23210,12 +23193,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
+++ b/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45E6336-AC6C-4183-85D6-0B29325654B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B25205-9B25-4383-BECB-E4CCC0C3112C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="37350" windowHeight="19740" firstSheet="1" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="735" yWindow="780" windowWidth="37665" windowHeight="20295" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -174,10 +174,6 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateFractionResidueRemoved">_xlfn.LAMBDA(_xlpm.TotalResidue,_xlpm.AmountRemoved, (_xlpm.AmountRemoved * 10 ^ 3) / (_xlpm.TotalResidue * 10 ^ 3))</definedName>
-    <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateHarvestIndex">_xlfn.LAMBDA(_xlpm.CropType,_xlpm.CropTypeArray,_xlpm.ResidueCropRatioArray, 1 / (1 + Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.CropType, _xlpm.CropTypeArray, _xlpm.ResidueCropRatioArray)))</definedName>
-    <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateResidueCropRatio">_xlfn.LAMBDA(_xlpm.HarvestIndex, (1 - _xlpm.HarvestIndex) / _xlpm.HarvestIndex)</definedName>
-    <definedName name="CommonCropping_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
@@ -241,145 +237,6 @@
     <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
     <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
     <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions">_xlfn.LAMBDA(_xlpm.MMS_ATMOS,_xlpm.EF_N2O,_xlpm.C_N2O, (_xlpm.MMS_ATMOS * _xlpm.EF_N2O * _xlpm.C_N2O) * 10 ^ -3)</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MMS_ATMOS","mass of N volatilised from MMS","kg N","Calculated from 4.1.1.5 (2)";"EF_N2O","nitrous oxide emission factor for atmospheric deposition","kg N2O-N/kg N","Constant";"C_N2O","factor to convert elemental mass of nitrous oxide to molecular mass","","Constant";"j","production system","","Input";"i","irrigation method","","Input";"r","rainfall zone","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_LatexEquation">_xlfn.LAMBDA("E_{N2O,ad}=(MMS_{ATMOS}\times EF_{N2O}\times C_{N2O})\times10^{-3}")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.5, Equation (1)")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_Title">_xlfn.LAMBDA("Total annual atmospheric deposition emissions from manure management")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_Unit">_xlfn.LAMBDA("t N2O")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__1_TotalAnnualAtmosphericDepositionEmissions_Variable">_xlfn.LAMBDA("E_N2Oad")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement">_xlfn.LAMBDA(_xlpm.MN_jmT,_xlpm.FracGASM_mT, _xlpm.MN_jmT * _xlpm.FracGASM_mT)</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MN_jmT","nitrogen in each treatment stage MMS (excluding MN_ijm13T2)","kg N","Calculated from 4.1.1.3 (2)(6)(8)";"FracGASM_mT","fraction of N volatilised in each MMS","(kg NH3-N + NOx-N)/kg N","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_LatexEquation">_xlfn.LAMBDA("MMS_{ATMOS}=\sum_{j}\sum_{m}\sum_{T}(MN_{jmT}\times FracGASM_{mT})")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.5, Equation (2)")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_Title">_xlfn.LAMBDA("Volatilised nitrogen from manure management")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_AtmosphericDeposition_Equations.VEERG_4_1_1_5__2_VolatilisedNitrogenFromManureManagement_Variable">_xlfn.LAMBDA("MMS_ATMOS")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1">_xlfn.LAMBDA(_xlpm.MN_jmT23,_xlpm.EF_mT23,_xlpm.FracGASM_mT23,_xlpm.PF, (_xlpm.MN_jmT23 * (1 - _xlpm.EF_mT23 - _xlpm.FracGASM_mT23)) * _xlpm.PF)</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MN_jmT23","mass of N in secondary and tertiary treatment MMS stages as calculated for manure management","kg N","Calculated from 4.1.1.3 (6)(8)";"EF_mT23","nitrous oxide emission factor for each MMS","kg N2O-N/kg N","Constant";"FracGASM_mT23","fraction of animal waste N volatilised in each MMS for each cattle group","(kg NH3-N + NOx-N)/kg N","Constant";"PF","fraction of manure applied to soil within the feedlot boundary","fraction","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_LatexEquation">_xlfn.LAMBDA("MNSoil_{scope1}=\sum_{j}\sum_{m}\sum_{T}(MN_{jmT=2,3}\times(1-EF_{mT=2,3}-FracGASM_{mT=2,3}))\times PF")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.9, Equation (1)")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_Title">_xlfn.LAMBDA("Mass of nitrogen applied to soils for scope 1 emissions")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__1_MassOfNitrogenAppliedToSoilsScope1_Variable">_xlfn.LAMBDA("MNSoil_scope1")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3">_xlfn.LAMBDA(_xlpm.MN_jmT23,_xlpm.EF_mT23,_xlpm.FracGASM_mT23,_xlpm.PF, (_xlpm.MN_jmT23 * (1 - _xlpm.EF_mT23 - _xlpm.FracGASM_mT23)) * (1 - _xlpm.PF))</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MN_jmT23","mass of N in secondary and tertiary treatment MMS stages as calculated for manure management","kg N","Calculated from 4.1.1.3 (6)(8)";"EF_mT23","nitrous oxide emission factor for each MMS","kg N2O-N/kg N","Constant";"FracGASM_mT23","fraction of animal waste N volatilised in each MMS for each cattle group","(kg NH3-N + NOx-N)/kg N","Constant";"PF","fraction of manure applied to soil within the feedlot boundary","fraction","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_LatexEquation">_xlfn.LAMBDA("MNSoil_{scope3}=\sum_{j}\sum_{m}\sum_{T}(MN_{jmT=2,3}\times(1-EF_{mT=2,3}-FracGASM_{mT=2,3}))\times(1-PF)")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.9, Equation (2)")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_Title">_xlfn.LAMBDA("Mass of nitrogen applied to soils for scope 3 emissions")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_ManureAppliedToSoils_Equations.VEERG_4_1_1_9__2_MassOfNitrogenAppliedToSoilsScope3_Variable">_xlfn.LAMBDA("MNSoil_scope3")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions">_xlfn.LAMBDA(_xlpm.D_j,_xlpm.M_jmT,_xlpm.N_j, (_xlpm.D_j * _xlpm.M_jmT * _xlpm.N_j) * 10 ^ -3)</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"D_j","length of stay of each cattle group","days","Input";"M_jmT","methane production from manure per cattle group, MMS, and treatment stage","kg CH4/head/day","Calculated from 4.1.1.1 (2)(3)(4)";"N_j","numbers of beef cattle in each group","head","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_LatexEquation">_xlfn.LAMBDA("{E}_{CH4}=\sum_{j}\sum_{m}\sum_{T}(D_{j}\times M_{jmT}\times N_{j})\times10^{-3}")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.1, Equation (1)")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Title">_xlfn.LAMBDA("Total annual methane emissions from manure management")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Unit">_xlfn.LAMBDA("t CH4")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__1_TotalAnnualMethaneEmissions_Variable">_xlfn.LAMBDA("E_CH4")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot">_xlfn.LAMBDA(_xlpm.VS_j,_xlpm.BO,_xlpm.MMS_m5T1,_xlpm.MCF_im5,_xlpm.rho, _xlfn.LET(_xlpm.MCF_im5, IF(ISNUMBER(_xlpm.MCF_im5), _xlpm.MCF_im5, 0), _xlpm.VS_j * _xlpm.BO * _xlpm.MMS_m5T1 * _xlpm.MCF_im5 * _xlpm.rho))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VS_j","volatile solid production from feedlot cattle in each group","kg/head/day","Calculated from 4.1.1.1 (5)";"BO","emissions potential","m3 CH4/kg VS","Constant";"MMS_m5T1","fraction of manure in primary system drylot MMS","fraction","Input";"MCF_im5","methane conversion factor for state and drylot system","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","state","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Arguments_Method2">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VS_j","volatile solid production from feedlot cattle in each group","kg/head/day","Calculated from 4.1.1.1 (5)";"BO","emissions potential","m3 CH4/kg VS","Constant";"MMS_m5T1","fraction of manure in primary system drylot MMS","fraction","Input";"MCF_im5","methane conversion factor for state and drylot system","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","state","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_LatexEquation">_xlfn.LAMBDA("M_{jm=5,T=1}=VS_{j}\times BO\times MMS_{m=5,T=1}\times MCF_{im=5}\times \rho")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.1, Equation (2)")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Title">_xlfn.LAMBDA("Production of methane in treatment stage 1 MMS")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Unit">_xlfn.LAMBDA("kg CH4/head/day")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__2_Stage1MethaneProductionDrylot_Variable">_xlfn.LAMBDA("M_jm5T1")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction">_xlfn.LAMBDA(_xlpm.VSL,_xlpm.VS_j,_xlpm.BO,_xlpm.MMS_mT2,_xlpm.MCF_im,_xlpm.rho, (1 - _xlpm.VSL) * _xlpm.VS_j * _xlpm.BO * _xlpm.MMS_mT2 * _xlpm.MCF_im * _xlpm.rho)</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(7, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VSL","fraction of volatile solids lost during storage in the primary system","fraction","Constant";"VS_j","volatile solid production from feedlot cattle in each group","kg/head/day","Calculated from 4.1.1.1 (5)";"BO","emissions potential","m3 CH4/kg VS","Constant";"MMS_mT2","fraction of manure in each secondary system","fraction","Input";"MCF_im","methane conversion factor for state and MMS","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","state","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Arguments_Method2">_xlfn.LAMBDA(_xlfn.MAKEARRAY(7, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VSL","fraction of volatile solids lost during storage in the primary system","fraction","Constant";"VS_j","volatile solid production from feedlot cattle in each group","kg/head/day","Calculated from 4.1.1.1 (5)";"BO","emissions potential","m3 CH4/kg VS","Constant";"MMS_mT2","fraction of manure in each secondary system","fraction","Input";"MCF_im","methane conversion factor for mean annual temperature and MMS","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","Mean annual temperature","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_LatexEquation">_xlfn.LAMBDA("M_{jmT=2}=(1-VSL)\times VS_{j}\times BO\times MMS_{mT=2}\times MCF_{im}\times \rho")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.1, Equation (3)")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Title">_xlfn.LAMBDA("Production of methane in treatment stage 2 MMS")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Unit">_xlfn.LAMBDA("kg CH4/head/day")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__3_Stage2MethaneProduction_Variable">_xlfn.LAMBDA("M_jmT2")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon">_xlfn.LAMBDA(_xlpm.VS_j,_xlpm.BO,_xlpm.MMS_m1T3,_xlpm.MCF_im1,_xlpm.rho, _xlpm.VS_j * _xlpm.BO * _xlpm.MMS_m1T3 * _xlpm.MCF_im1 * _xlpm.rho)</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VS_j","volatile solid production from feedlot cattle in each group j","kg/head/day","Calculated from 4.1.1.1 (5)";"BO","emissions potential","m3 CH4/kg VS","Constant";"MMS_m1T3","fraction of manure to tertiary anaerobic lagoon system","fraction","Input";"MCF_im1","methane conversion factor for state and anaerobic lagoon system","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","state","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_Arguments_Method2">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VS_j","volatile solid production from feedlot cattle in each group j","kg/head/day","Calculated from 4.1.1.1 (5)";"BO","emissions potential","m3 CH4/kg VS","Constant";"MMS_m1T3","fraction of manure to tertiary anaerobic lagoon system","fraction","Input";"MCF_im1","methane conversion factor for mean annual temperature and anaerobic lagoon system","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","Mean annual temperature","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_LatexEquation">_xlfn.LAMBDA("M_{jm=1,T=3}=VS_{j}\times BO\times MMS_{m=1,T=3}\times MCF_{im=1}\times \rho")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.1, Equation (4)")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_Title">_xlfn.LAMBDA("Production of methane in treatment stage 3 MMS")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_Unit">_xlfn.LAMBDA("kg CH4/head/day")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__4_Stage3MethaneProductionAnaerobicLagoon_Variable">_xlfn.LAMBDA("M_jm1T3")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction">_xlfn.LAMBDA(_xlpm.I_j,_xlpm.DMD_j,_xlpm.A, _xlpm.I_j * (1 - _xlpm.DMD_j) * (1 - _xlpm.A))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_j","dry matter intake for each group j","kg DM/head/day","Input";"DMD_j","dry matter digestibility for each group j","fraction","Input";"A","ash content of manure","fraction","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_LatexEquation">_xlfn.LAMBDA("VS_{j}=I_{j}\times(1-DMD_{j})\times(1-A)")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.1, Equation (5)")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_Title">_xlfn.LAMBDA("Volatile solid production")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_Unit">_xlfn.LAMBDA("kg/head/day")</definedName>
-    <definedName name="MMS_Feedlot_Methane_Equations.VEERG_4_1_1_1__5_VolatileSolidProduction_Variable">_xlfn.LAMBDA("VS_j")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions">_xlfn.LAMBDA(_xlpm.MN_jmT,_xlpm.EF_jm,_xlpm.C_N2O, SUMPRODUCT(_xlpm.MN_jmT, _xlpm.EF_jm, _xlpm.C_N2O) * 10 ^ -3)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MN_jmT","nitrogen per cattle group, MMS and treatment stage","kg N","Calculated from 4.1.1.3 (2)(6)(8)";"EF_jm","nitrous oxide emission factor for MMS","kg N2O-N/kg N","Constant";"C_N2O","factor to convert elemental mass of nitrous oxide to molecular mass","ratio","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_LatexEquation">_xlfn.LAMBDA("E_{N2O,dir}=\sum_{j}\sum_{m}\sum_{T}(MN_{jmT}\times EF_{jm}\times C_{N2O})\times10^{-3}")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (1)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_Title">_xlfn.LAMBDA("Total annual direct nitrous oxide emissions from manure management systems")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_Unit">_xlfn.LAMBDA("t N2O")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__1_TotalAnnualDirectNitrousOxideEmissions_Variable">_xlfn.LAMBDA("E_N2Odir")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot">_xlfn.LAMBDA(_xlpm.AE_j,_xlpm.MMS_jm5T1, _xlpm.AE_j * _xlpm.MMS_jm5T1)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"AE_j","total nitrogen excreted by each cattle group","kg N","Calculated from 4.1.1.3 (3)";"MMS_jm5T1","fraction of manure in primary system drylot MMS","fraction","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_LatexEquation">_xlfn.LAMBDA("MN_{jm=5,T=1}=AE_{j}\times MMS_{jm=5,T=1}")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (2)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_Title">_xlfn.LAMBDA("Nitrogen in treatment stage 1 MMS")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__2_Stage1NitrogenInMMSDrylot_Variable">_xlfn.LAMBDA("MN_jm5T1")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion">_xlfn.LAMBDA(_xlpm.N_j,_xlpm.NE_j,_xlpm.D_j, _xlpm.N_j * _xlpm.NE_j * _xlpm.D_j)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"N_j","number of cattle in each group","head","Input";"NE_j","nitrogen excretion","kg N/head/day","Calculated from 4.1.1.3 (4)";"D_j","duration of stay of cattle group","days","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_LatexEquation">_xlfn.LAMBDA("AE_{j}=N_{j}\times NE_{j}\times D_{j}")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (3)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_Title">_xlfn.LAMBDA("Annual nitrogen excretion from each feedlot cattle group")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__3_AnnualNitrogenExcretion_Variable">_xlfn.LAMBDA("AE_j")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead">_xlfn.LAMBDA(_xlpm.NI_j,_xlpm.NR_j, _xlpm.NI_j * (1 - _xlpm.NR_j))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"NI_j","nitrogen intake","kg N/head/day","Calculated from 4.1.1.3 (5)";"NR_j","nitrogen retention expressed as a fraction of intake","fraction","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_LatexEquation">_xlfn.LAMBDA("NE_{j}=NI_{j}\times(1-NR_{j})")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (4)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_Title">_xlfn.LAMBDA("Nitrogen excretion per head per day")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_Unit">_xlfn.LAMBDA("kg N/head/day")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__4_NitrogenExcretionPerHead_Variable">_xlfn.LAMBDA("NE_j")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake">_xlfn.LAMBDA(_xlpm.I_j,_xlpm.CP_j, _xlpm.I_j * _xlpm.CP_j / 6.25)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_j","dry matter intake","kg DM/head/day","Input";"CP_j","crude protein content of feed","fraction","Input";"6.25","factor for converting crude protein into nitrogen","ratio","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_LatexEquation">_xlfn.LAMBDA("NI_{j}=I_{j}\times CP_{j}\div 6.25")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (5)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_Title">_xlfn.LAMBDA("Nitrogen intake of feedlot cattle")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_Unit">_xlfn.LAMBDA("kg N/head/day")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__5_NitrogenIntake_Variable">_xlfn.LAMBDA("NI_j")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS">_xlfn.LAMBDA(_xlpm.NT_jmT2,_xlpm.MMS_jmT2, _xlpm.NT_jmT2 * _xlpm.MMS_jmT2)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"NT_jmT2","nitrogen transferred to secondary treatment MMS","kg N","Calculated from 4.1.1.3 (7)";"MMS_jmT2","fraction of manure in each secondary system","fraction","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_LatexEquation">_xlfn.LAMBDA("MN_{jm,T=2}=NT_{jm,T=2}\times MMS_{jm,T=2}")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (6)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_Title">_xlfn.LAMBDA("Nitrogen in treatment stage 2 MMS")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__6_Stage2NitrogenInMMS_Variable">_xlfn.LAMBDA("MN_jmT2")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2">_xlfn.LAMBDA(_xlpm.MN_jm5T1,_xlpm.FracGASM_m5,_xlpm.EF_m5,_xlpm.MN_jmT3, (_xlpm.MN_jm5T1 * (1 - _xlpm.FracGASM_m5 - _xlpm.EF_m5)) - _xlpm.MN_jmT3)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MN_jm5T1","nitrogen in MMS treatment stage 1","kg N","Calculated from 4.1.1.3 (2)";"FracGASM_m5","fraction of N volatilised from drylot MMS","fraction","Constant";"EF_m5","nitrous oxide emission factor for drylot MMS","kg N2O-N/kg N deposited","Constant";"MN_jmT3","nitrogen in MMS treatment stage 3","kg N","Calculated from 4.1.1.3 (8)"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_LatexEquation">_xlfn.LAMBDA("NT_{jm,T=2}=(MN_{jm=5,T=1}\times(1-FracGASM_{m=5}-EF_{m=5}))-MN_{jm,T=3}")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (7)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_Title">_xlfn.LAMBDA("Nitrogen transferred to treatment stage 2 MMS")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__7_NitrogenTransferredToStage2_Variable">_xlfn.LAMBDA("NT_jmT2")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon">_xlfn.LAMBDA(_xlpm.AE_j,_xlpm.MMS_jm1T3, _xlpm.AE_j * _xlpm.MMS_jm1T3)</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"AE_j","total nitrogen excreted by each cattle group","kg N","Calculated from 4.1.1.3 (3)";"MMS_jm1T3","fraction of manure to tertiary anaerobic lagoon system","fraction","Input"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_LatexEquation">_xlfn.LAMBDA("MN_{jm=1,T=3}=AE_{j}\times MMS_{jm=1,T=3}")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_NIRReference">_xlfn.LAMBDA("")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_Source">_xlfn.LAMBDA("VEERG 2026: 4.1.1.3, Equation (8)")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_Title">_xlfn.LAMBDA("Nitrogen in treatment stage 3 MMS")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_Unit">_xlfn.LAMBDA("kg N")</definedName>
-    <definedName name="MMS_Feedlot_N2ODirect_Equations.VEERG_4_1_1_3__8_Stage3NitrogenInMMSAnaerobicLagoon_Variable">_xlfn.LAMBDA("MN_jm1T3")</definedName>
     <definedName name="Range_LivestockStartingValues">#REF!</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(10, 7, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Feedlot type","Characteristic","Unit","2005-2009","2010-2014","2015-2019","2020-2023";"Domestic","Days on feed","days",70,70,70,75;"Domestic","Feed intake","kg DM/day",10,10,10.4,10.4;"Domestic","N retention","per cent of intake",21.1,20.4,20.4,20.4;"Mid-fed","Days on feed","days",115,115,120,150;"Mid-fed","Feed intake","kg DM/day",11.2,10.8,10.8,10.8;"Mid-fed","N retention","per cent of intake",12.5,12.7,12.7,12.7;"Long-fed","Days on feed","days",250,250,250,250;"Long-fed","Feed intake","kg DM/day",9,8.5,8.2,8.2;"Long-fed","N retention","per cent of intake",6.6,7,7,7}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.1.2: Beef feedlot cattle - Animal characteristics")</definedName>
@@ -782,9 +639,6 @@
     <t>MMS m</t>
   </si>
   <si>
-    <t>Input - MMS - Feedlot</t>
-  </si>
-  <si>
     <t>kg dry matter / head  day</t>
   </si>
   <si>
@@ -933,9 +787,6 @@
   </si>
   <si>
     <t>Scope 1 source</t>
-  </si>
-  <si>
-    <t>4.1.1.1-2 Manure Methane</t>
   </si>
   <si>
     <t>Production system j</t>
@@ -1177,6 +1028,12 @@
   </si>
   <si>
     <t>💡 Below is a diagram that maps the equations used to calculate emissions and how they interact with each other.</t>
+  </si>
+  <si>
+    <t>3.1.1.1-2 Enteric Methane Beef Feedlot</t>
+  </si>
+  <si>
+    <t>Input - Feedlot</t>
   </si>
 </sst>
 </file>
@@ -3366,6 +3223,32 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB2D498"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3483,32 +3366,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB2D498"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6016,22 +5873,22 @@
     <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6147,49 +6004,49 @@
     <tableColumn id="1" xr3:uid="{25162FA7-7F7F-4C9C-8231-8FC51C581FD1}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6207,7 +6064,7 @@
     <tableColumn id="1" xr3:uid="{2BBE1D44-5D3C-421E-B886-5F058BD82B23}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6311,7 +6168,7 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="57" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="52" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6327,7 +6184,7 @@
     <tableColumn id="1" xr3:uid="{ACC4E2B3-A6FC-4D50-BE90-6D711BFC3B97}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="23">
+    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="18">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6375,7 +6232,7 @@
     <tableColumn id="1" xr3:uid="{6328C683-420D-4EA6-AF9D-245995DC8FD1}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6393,7 +6250,7 @@
     <tableColumn id="1" xr3:uid="{FB787692-FEAA-422C-9A68-A116E1C1D839}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6411,7 +6268,7 @@
     <tableColumn id="1" xr3:uid="{E0DBFFCC-335E-4C29-BC47-5C2A3243CFF0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6443,49 +6300,49 @@
     <tableColumn id="1" xr3:uid="{8C0CBC0D-B831-4C7E-9F24-0EE0037F3E6B}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6530,22 +6387,22 @@
     <tableColumn id="1" xr3:uid="{FDCB848C-205F-48EA-BACF-F54BCD324E05}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6568,22 +6425,22 @@
     <tableColumn id="1" xr3:uid="{96F6B4E3-E1EE-445F-9BCE-628B89FC3727}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6601,7 +6458,7 @@
     <tableColumn id="1" xr3:uid="{9D472457-4D8B-44ED-9567-B889D058C2F1}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6621,13 +6478,13 @@
     <tableColumn id="1" xr3:uid="{C80C08D8-3F48-4E18-98E3-9B53ACB6C6D9}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6636,7 +6493,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="40" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D112:G117" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6910,7 +6767,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="503" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="882" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -6962,7 +6819,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -7360,7 +7217,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="109" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D1" s="110"/>
       <c r="E1" s="110"/>
@@ -7570,7 +7427,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="112" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E5" s="112"/>
       <c r="F5" s="112"/>
@@ -7637,7 +7494,7 @@
       <c r="A6" s="16"/>
       <c r="C6" s="1"/>
       <c r="D6" s="113" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E6" s="114"/>
       <c r="F6" s="114"/>
@@ -12636,7 +12493,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="102" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12697,25 +12554,25 @@
       <c r="A6" s="16"/>
       <c r="C6" s="24"/>
       <c r="D6" s="100" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" s="100" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="100" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="100" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="H6" s="100" t="s">
+      <c r="I6" s="100" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="100" t="s">
-        <v>145</v>
-      </c>
       <c r="J6" s="100" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
@@ -12726,7 +12583,7 @@
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E7" s="98">
         <f>'3.1.1.1-2 Enteric Methane'!E67</f>
@@ -12749,7 +12606,7 @@
         <v>991.7664400000001</v>
       </c>
       <c r="J7" s="52" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
@@ -12761,7 +12618,7 @@
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="31"/>
@@ -12775,7 +12632,7 @@
         <v>991.7664400000001</v>
       </c>
       <c r="J8" s="93" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
@@ -14670,7 +14527,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="N1" s="54"/>
       <c r="O1" s="54"/>
@@ -14719,7 +14576,7 @@
         <v>Results</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -14731,13 +14588,13 @@
       </c>
       <c r="D7" s="58"/>
       <c r="E7" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="G7" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -14759,7 +14616,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -14784,7 +14641,7 @@
         <v>250</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -14809,16 +14666,16 @@
     </row>
     <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E13" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="G13" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -14826,7 +14683,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="50" cm="1">
         <f t="array" ref="E14">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_AnimalCharacteristics[Feedlot type] = E$13) * (Table_SourceData_Feedlot_AnimalCharacteristics[Characteristic] = $D$14), Table_SourceData_Feedlot_AnimalCharacteristics[2020-2023], "Not Found")</f>
@@ -14841,7 +14698,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -14853,7 +14710,7 @@
         <v>Constants - Feedlot</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E15" s="50" cm="1">
         <f t="array" ref="E15">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$13) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$15), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14868,7 +14725,7 @@
         <v>5.5</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -14880,7 +14737,7 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E16" s="50" cm="1">
         <f t="array" ref="E16">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$13) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$16), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14895,7 +14752,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -14915,21 +14772,21 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E18" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="G18" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="61" cm="1">
         <f t="array" ref="E19">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_AnimalCharacteristics[Feedlot type] = E$18) * (Table_SourceData_Feedlot_AnimalCharacteristics[Characteristic] = $D$19), Table_SourceData_Feedlot_AnimalCharacteristics[2020-2023], "Not Found")</f>
@@ -14944,13 +14801,13 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E20" s="61" cm="1">
         <f t="array" ref="E20">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$18) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$20), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14965,7 +14822,7 @@
         <v>5.5</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -14974,7 +14831,7 @@
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="D21" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E21" s="61" cm="1">
         <f t="array" ref="E21">_xlfn.XLOOKUP(1, (Table_SourceData_Feedlot_DietProperties[Feedlot type] = E$18) * (Table_SourceData_Feedlot_DietProperties[Nutrient analysis] = $D$21), Table_SourceData_Feedlot_DietProperties[2020-2023 Converted to fraction], "Not Found")</f>
@@ -14989,7 +14846,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -15225,7 +15082,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="K1"/>
     </row>
@@ -15239,7 +15096,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -15249,7 +15106,7 @@
       <c r="J3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -15411,10 +15268,10 @@
         <v>Constants - Common</v>
       </c>
       <c r="D17" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="86" t="s">
         <v>109</v>
-      </c>
-      <c r="M17" s="86" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15423,30 +15280,30 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D18" s="85" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="85" t="s">
         <v>113</v>
-      </c>
-      <c r="M18" s="85" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="F19" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="39" t="s">
-        <v>101</v>
-      </c>
       <c r="M19" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="N19" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="N19" s="39" t="s">
+      <c r="O19" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="O19" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15488,38 +15345,38 @@
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="86" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M22" s="86" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="85" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M23" s="85" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="F24" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="39" t="s">
-        <v>101</v>
-      </c>
       <c r="M24" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="N24" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="N24" s="39" t="s">
+      <c r="O24" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="O24" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15560,38 +15417,38 @@
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="86" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M27" s="86" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="85" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M28" s="85" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E29" s="39" t="s">
+      <c r="F29" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="39" t="s">
-        <v>101</v>
-      </c>
       <c r="M29" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="N29" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="N29" s="39" t="s">
+      <c r="O29" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="O29" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15631,38 +15488,38 @@
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="86" t="s">
+        <v>169</v>
+      </c>
+      <c r="M32" s="86" t="s">
         <v>171</v>
-      </c>
-      <c r="M32" s="86" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="33" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="85" t="s">
+        <v>170</v>
+      </c>
+      <c r="M33" s="85" t="s">
         <v>172</v>
-      </c>
-      <c r="M33" s="85" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="34" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="F34" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="F34" s="49" t="s">
-        <v>101</v>
-      </c>
       <c r="M34" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="N34" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="N34" s="49" t="s">
+      <c r="O34" s="49" t="s">
         <v>100</v>
-      </c>
-      <c r="O34" s="49" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="35" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15825,23 +15682,23 @@
     <row r="51" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="86" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E54" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E54" s="39" t="s">
+      <c r="F54" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="F54" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="55" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15865,23 +15722,23 @@
     <row r="56" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E59" s="39" t="s">
+      <c r="F59" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="F59" s="39" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="60" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15905,38 +15762,38 @@
     <row r="61" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M62" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M63" s="85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="4:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="49" t="s">
+      <c r="F64" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="F64" s="49" t="s">
-        <v>101</v>
-      </c>
       <c r="M64" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="N64" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="N64" s="49" t="s">
+      <c r="O64" s="49" t="s">
         <v>100</v>
-      </c>
-      <c r="O64" s="49" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="65" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15976,7 +15833,7 @@
     <row r="66" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="89" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E67" s="90">
         <f>SUM(D65:F65)</f>
@@ -15987,7 +15844,7 @@
         <v>t CH4</v>
       </c>
       <c r="M67" s="89" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N67" s="90">
         <f>SUM(M65:O65)</f>
@@ -16060,7 +15917,7 @@
     <row r="71" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E72" s="45" cm="1">
         <f t="array" ref="E72">Common_Equations.Common_ConvertCH4ToCO2e(G69,G70)</f>
@@ -16071,7 +15928,7 @@
         <v>t CO2e</v>
       </c>
       <c r="M72" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N72" s="45" cm="1">
         <f t="array" ref="N72">Common_Equations.Common_ConvertCH4ToCO2e(P69,P70)</f>
@@ -16222,7 +16079,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16445,13 +16302,13 @@
     <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="D25" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G25" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="M25" s="1"/>
     </row>
@@ -16466,10 +16323,10 @@
         <v>63</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J27" s="37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M27" s="1"/>
     </row>
@@ -16487,7 +16344,7 @@
         <v>Crop</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M28" s="1"/>
     </row>
@@ -16505,7 +16362,7 @@
         <v>Pasture</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M29" s="1"/>
     </row>
@@ -16519,7 +16376,7 @@
         <v>Composting (passive windrow) (m=6)</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M30" s="1"/>
     </row>
@@ -16533,7 +16390,7 @@
         <v>Direct application (m=13)</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M31" s="1"/>
     </row>
@@ -16547,7 +16404,7 @@
         <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M32" s="1"/>
     </row>
@@ -16576,10 +16433,10 @@
     </row>
     <row r="38" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M38" s="1"/>
     </row>
@@ -16657,25 +16514,25 @@
     </row>
     <row r="49" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E49" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F49" s="37" t="s">
         <v>11</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H49" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I49" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="I49" s="37" t="s">
+      <c r="J49" s="37" t="s">
         <v>96</v>
-      </c>
-      <c r="J49" s="37" t="s">
-        <v>97</v>
       </c>
       <c r="M49" s="24"/>
     </row>
@@ -16999,25 +16856,25 @@
     </row>
     <row r="66" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>93</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>94</v>
       </c>
       <c r="F66" s="37" t="s">
         <v>11</v>
       </c>
       <c r="G66" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H66" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="H66" s="37" t="s">
+      <c r="I66" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="I66" s="37" t="s">
-        <v>97</v>
-      </c>
       <c r="J66" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M66" s="24"/>
     </row>
@@ -17443,7 +17300,7 @@
     </row>
     <row r="88" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E88" s="37" t="s">
         <v>80</v>
@@ -17741,13 +17598,13 @@
     </row>
     <row r="100" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E100" s="37" t="s">
         <v>80</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G100" s="37" t="s">
         <v>78</v>
@@ -17887,13 +17744,13 @@
     </row>
     <row r="112" spans="4:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E112" s="95" t="s">
         <v>80</v>
       </c>
       <c r="F112" s="95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G112" s="95" t="s">
         <v>78</v>
@@ -20273,7 +20130,7 @@
     </row>
     <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E142" s="37" t="s">
         <v>75</v>
@@ -20633,16 +20490,16 @@
     </row>
     <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E186" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="F186" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="E186" s="37" t="s">
+      <c r="G186" s="37" t="s">
         <v>120</v>
-      </c>
-      <c r="F186" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="G186" s="37" t="s">
-        <v>122</v>
       </c>
       <c r="H186" s="37" t="s">
         <v>25</v>
@@ -20963,7 +20820,7 @@
         <v>8</v>
       </c>
       <c r="E206" s="37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
@@ -20994,10 +20851,10 @@
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D212" s="37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E212" s="37" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
@@ -21143,49 +21000,49 @@
         <v>42</v>
       </c>
       <c r="E231" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F231" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="G231" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="F231" s="36" t="s">
+      <c r="H231" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="G231" s="37" t="s">
+      <c r="I231" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="H231" s="37" t="s">
+      <c r="J231" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="I231" s="37" t="s">
+      <c r="K231" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="J231" s="37" t="s">
+      <c r="L231" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="K231" s="37" t="s">
+      <c r="M231" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="L231" s="37" t="s">
+      <c r="N231" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="M231" s="37" t="s">
+      <c r="O231" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="N231" s="37" t="s">
+      <c r="P231" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="O231" s="37" t="s">
+      <c r="Q231" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="R231" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="P231" s="37" t="s">
+      <c r="S231" s="37" t="s">
         <v>160</v>
-      </c>
-      <c r="Q231" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="R231" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="S231" s="37" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
@@ -23159,7 +23016,7 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMATABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA1ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AFwAbgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA2ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA5ACkAOwBcAG4AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAE0ATQBTAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABtAGkAZAAgAGYAZQBkAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbABvAG4AZwAgAGYAZQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATABlAG4AZwB0AGgAIABvAGYAIABTAHQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAMQAtADgAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAOAAxAC0AMgAwADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIAMgAwADEAKwAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBhAG0AZQBkACAAJwBjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAJwAgAGMAbwBsAHUAbQBuACAALQAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAYQBzACAAaABlAGEAZABlAHIAIAAnAFUAbgBpAHQAJwAgAHcAaABpAGMAaAAgAGMAbwB2AGUAcgBzACAAdAB3AG8AIABjAG8AbAB1AG0AbgBzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAANwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAANwAwACwAIAA3ADAALAAgADcAMAAsACAANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADAALgAwACwAIAAxADAALgAwACwAIAAxADAALgA0ACwAIAAxADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAyADEALgAxACwAIAAyADAALgA0ACwAIAAyADAALgA0ACwAIAAyADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADEAMQA1ACwAIAAxADEANQAsACAAMQAyADAALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAxAC4AMgAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADEAMgAuADUALAAgADEAMgAuADcALAAgADEAMgAuADcALAAgADEAMgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAOQAuADAALAAgADgALgA1ACwAIAA4AC4AMgAsACAAOAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADYALgA2ACwAIAA3AC4AMAAsACAANwAuADAALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgAgAGMAbwBsAHUAbQBuACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AGUAZAAgAE4ARABGACAAYQBuAGQAIABFAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAdgBhAGwAdQBlAHMAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAA4ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgAzAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA0AC4ANQAsACAANAAuADUALAAgADQALgA4ACwAIAA0AC4AOAAsACAAMAAuADAANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAwAC4AMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADUALAAgADUALgA1ACwAIAAwAC4AMAA1ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABjAG8AbAB1AG0AbgAgAHQAaABhAHQAIABkAHUAcABsAGkAYwBhAHQAZQBzACAAUQBMAEQAIAB2AGEAbAB1AGUAcwAgAGEAcwAgAHAAZQByACAAYQBkAHYAaQBjAGUAIABmAHIAbwBtACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAcAByAG8AdgBpAGQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AIAB0AGgAYQB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAgAFYASQBDACAAdgBhAGwAdQBlAHMAIABhAHMAIABwAGUAcgAgAGEAZAB2AGkAYwBlACAAZgByAG8AbQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHAAcgBvAHYAaQBkAGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBFAEYAbQBUACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADAANQA0ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADAAMAA1ACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgAwADEALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAFAAbwBuAGQAKQBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADYAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADYAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgA2ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4ANAAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADMANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAXwBqACAAPQAgAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgBNAF8AagBtAFQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqAG0AVAAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqAG0AVAAgACoAIABOAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsAFwAIgBsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADIAKQAoADMAKQAoADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0AXwBqAG0ANQBUADEAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQA1AH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtADUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0ANQBUADEALAAgAE0AQwBGAF8AaQBtADUALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBDAEYAXwBpAG0ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBDAEYAXwBpAG0ANQApACwAIABNAEMARgBfAGkAbQA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADUAVAAxACAAKgAgAE0AQwBGAF8AaQBtADUAIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQA1AFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADUAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAZQAgAGEAbgBkACAAZAByAHkAbABvAHQAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0ANQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBfAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0AVAA9ADIAfQA9ACgAMQAtAFYAUwBMACkAXABcAHQAaQBtAGUAcwAgAFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMATAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAF8AaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAGEAbgBkACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMATAAsACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0AVAAyACwAIABNAEMARgBfAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIAAoADEAIAAtACAAVgBTAEwAKQAgACoAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AVAAyACAAKgAgAE0AQwBGAF8AaQBtACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBfAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcABcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAZQAgAGEAbgBkACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMQAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAXAAiACwAIABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABhAG4AZAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIALAAgAFwAIgBrAGcALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAE0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcAG4ATQBfAGoAbQAxAFQAMwBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0AMQBUADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBfAGkAbQAxACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAGEAbgBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0AMQBUADMALAAgAE0AQwBGAF8AaQBtADEALAAgAHIAaABvACwAXABuACAAIAAgACAAVgBTAF8AagAgACoAIABCAE8AIAAqACAATQBNAFMAXwBtADEAVAAzACAAKgAgAE0AQwBGAF8AaQBtADEAIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBtADEAVAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAXwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADQALgAxAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBfAGkAbQAxAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACwAIABcACIAawBnAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAagBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIALAAgAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AbQAxAFQAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AMQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAGsAZwAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIATQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAFMAXwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBBACAAPQAgAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABEAE0ARABfAGoALAAgAEEALABcAG4AIAAgACAAIABJAF8AagAgACoAIAAoADEAIAAtACAARABNAEQAXwBqACkAIAAqACAAKAAxACAALQAgAEEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAXwB7AGoAfQA9AEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAEEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0ARABfAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAagBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAFwAIgAsAFwAIgBhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADkAIABNAGEAbgB1AHIAZQAgAEEAcABwAGwAaQBlAGQAIAB0AG8AIABTAG8AaQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMQBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAxAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACAAUABGAFwAbgBNAE4AXwBqAG0AVAAyADMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyADMAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGYAZQBlAGQAbABvAHQAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIAMwAsACAARQBGAF8AbQBUADIAMwAsACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAsACAAUABGACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0AVAAyADMAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyADMAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwApACkAIAAqACAAUABGAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADEAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABQAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAMwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgAsAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANgApACgAOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBOAFMAbwBpAGwAXwBzAGMAbwBwAGUAMwBcAG4AawBnACAATgBcAG4ATQBOAFMAbwBpAGwAXwB7AHMAYwBvAHAAZQAzAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAPQAyACwAMwB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARQBGAF8AewBtAFQAPQAyACwAMwB9AC0ARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAPQAyACwAMwB9ACkAKQBcAFwAdABpAG0AZQBzACgAMQAtAFAARgApAFwAbgBNAE4AXwBqAG0AVAAyADMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAG0AVAAyADMAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABhAG4AaQBtAGEAbAAgAHcAYQBzAHQAZQAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAFAARgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAGYAZQBlAGQAbABvAHQAIABiAG8AdQBuAGQAYQByAHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUADIAMwAsACAARQBGAF8AbQBUADIAMwAsACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwAsACAAUABGACwAXABuACAAIAAgACAAKABNAE4AXwBqAG0AVAAyADMAIAAqACAAKAAxACAALQAgAEUARgBfAG0AVAAyADMAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQBUADIAMwApACkAIAAqACAAKAAxACAALQAgAFAARgApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHMAYwBvAHAAZQAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADkALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AUwBvAGkAbABfAHsAcwBjAG8AcABlADMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAA9ADIALAAzAH0AXABcAHQAaQBtAGUAcwAoADEALQBFAEYAXwB7AG0AVAA9ADIALAAzAH0ALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAA9ADIALAAzAH0AKQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AUABGACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADIAMwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIABzAGUAYwBvAG4AZABhAHIAeQAgAGEAbgBkACAAdABlAHIAdABpAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwAgAHMAdABhAGcAZQBzACAAYQBzACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAbwByACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgAsAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANgApACgAOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFQAMgAzAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0AVAAyADMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGEAbgBpAG0AYQBsACAAdwBhAHMAdABlACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAZgBlAGUAZABsAG8AdAAgAGIAbwB1AG4AZABhAHIAeQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxADoAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEALgAxAC4ANQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAEQAZQBwAG8AcwBpAHQAaQBvAG4AIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBfAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGEAZAB9AD0AKABNAE0AUwBfAHsAQQBUAE0ATwBTAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBNAFMAXwBBAFQATQBPAFMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAATQBNAFMAIAA6ACAAawBnACAATgBcAG4ARQBGAF8ATgAyAE8AIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAF8AQQBUAE0ATwBTACwAIABFAEYAXwBOADIATwAsACAAQwBfAE4AMgBPACwAXABuACAAIAAgACAAKABNAE0AUwBfAEEAVABNAE8AUwAgACoAIABFAEYAXwBOADIATwAgACoAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADUALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8ALABhAGQAfQA9ACgATQBNAFMAXwB7AEEAVABNAE8AUwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgA1ACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAE4AMgBPAFwAIgAsAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAFwAIgAsACAAXAAiAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4AVgBvAGwAYQB0AGkAbABpAHMAZQBkACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ATQBNAFMAXwBBAFQATQBPAFMAXABuAGsAZwAgAE4AXABuAE0ATQBTAF8AewBBAFQATQBPAFMAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgATQBOAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAEcAQQBTAE0AXwB7AG0AVAB9ACkAXABuAE0ATgBfAGoAbQBUACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAE0ATgBfAGkAagBtADEAMwBUADIAKQAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGkAbgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQALABcAG4AIAAgACAAIABNAE4AXwBqAG0AVAAgACoAIABGAHIAYQBjAEcAQQBTAE0AXwBtAFQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAG4AaQB0AHIAbwBnAGUAbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAXwBBAFQATQBPAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgA1ACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBfAHsAQQBUAE0ATwBTAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBHAEEAUwBNAF8AewBtAFQAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAF8AagBtAFQAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAE0ATQBTACAAKABlAHgAYwBsAHUAZABpAG4AZwAgAE0ATgBfAGkAagBtADEAMwBUADIAKQBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgAMgApACgANgApACgAOAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AXwBtAFQAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABpAG4AIABlAGEAYwBoACAATQBNAFMAXAAiACwAIABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADMAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABEAGkAcgBlAGMAdAAgAE4AMgBPACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAHMAXABuAEUAXwBOADIATwBkAGkAcgBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwAsAGQAaQByAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqAG0AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ATQBOAF8AagBtAFQAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAE4AXABuAEUARgBfAGoAbQAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAE0ATQBTACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXABuAEMAXwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAHIAYQB0AGkAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQBUACwAIABFAEYAXwBqAG0ALAAgAEMAXwBOADIATwAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABNAE4AXwBqAG0AVAAsACAARQBGAF8AagBtACwAIABDAF8ATgAyAE8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AZABpAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwAsAGQAaQByAH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAE0ATgBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBqAG0AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0AVABcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAcABlAHIAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAsACAATQBNAFMAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAyACkAKAA2ACkAKAA4ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoAbQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABNAE0AUwBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAXwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALABcACIAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0ATgBfAGoAbQA1AFQAMQBcAG4AawBnACAATgBcAG4ATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQA9AEEARQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABuAEEARQBfAGoAIAA9ACAAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0ANQBUADEALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADUAVAAxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADUAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADUAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFwAbgBBAG4AbgB1AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAZgByAG8AbQAgAGUAYQBjAGgAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXABuAEEARQBfAGoAXABuAGsAZwAgAE4AXABuAEEARQBfAHsAagB9AD0ATgBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABOAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagB9AFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAbgBOAEUAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAEQAXwBqACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoALAAgAE4ARQBfAGoALAAgAEQAXwBqACwAXABuACAAIAAgACAATgBfAGoAIAAqACAATgBFAF8AagAgACoAIABEAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbgBuAHUAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAaQBvAG4AIABmAHIAbwBtACAAZQBhAGMAaAAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBFAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEUAXwB7AGoAfQA9AE4AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATgBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBfAGoAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgBOAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABpAG8AbgAgAHAAZQByACAAaABlAGEAZAAgAHAAZQByACAAZABhAHkAXABuAE4ARQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ARQBfAHsAagB9AD0ATgBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBOAFIAXwB7AGoAfQApAFwAbgBOAEkAXwBqACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAOgAgAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AUgBfAGoAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAcgBlAHQAZQBuAHQAaQBvAG4AIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AdABhAGsAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4ASQBfAGoALAAgAE4AUgBfAGoALABcAG4AIAAgACAAIABOAEkAXwBqACAAKgAgACgAMQAgAC0AIABOAFIAXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGkAbwBuACAAcABlAHIAIABoAGUAYQBkACAAcABlAHIAIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBFAF8AewBqAH0APQBOAEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAE4AUgBfAHsAagB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEkAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABOAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFIAXwBqAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuAHQAYQBrAGUAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAXABuAE4ASQBfAGoAXABuAGsAZwAgAE4ALwBoAGUAYQBkAC8AZABhAHkAXABuAE4ASQBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABDAFAAXwB7AGoAfQBcAFwAZABpAHYAIAA2AC4AMgA1AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBDAFAAXwBqACAAPQAgAGMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuADYALgAyADUAIAA9ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHYAZQByAHQAaQBuAGcAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAaQBuAHQAbwAgAG4AaQB0AHIAbwBnAGUAbgAgADoAIAByAGEAdABpAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAAQwBQAF8AagAsAFwAbgAgACAAIAAgAEkAXwBqACAAKgAgAEMAUABfAGoAIAAvACAANgAuADIANQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgB0AGEAawBlACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAzACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ASQBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABDAFAAXwB7AGoAfQBcAFwAZABpAHYAIAA2AC4AMgA1AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBQAF8AagBcACIALABcACIAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADYALgAyADUAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB2AGUAcgB0AGkAbgBnACAAYwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGkAbgB0AG8AIABuAGkAdAByAG8AZwBlAG4AXAAiACwAIABcACIAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4ATgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0ATgBfAGoAbQBUADIAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABuAE4AVABfAGoAbQBUADIAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAcwBlAGMAbwBuAGQAYQByAHkAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAE0ATQBTACAAOgAgAGsAZwAgAE4AXABuAE0ATQBTAF8AagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACwAIABNAE0AUwBfAGoAbQBUADIALABcAG4AIAAgACAAIABOAFQAXwBqAG0AVAAyACAAKgAgAE0ATQBTAF8AagBtAFQAMgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AZwBlAG4AIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMwAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBfAHsAagBtACwAVAA9ADIAfQA9AE4AVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABfAGoAbQBUADIAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAdAByAGUAYQB0AG0AZQBuAHQAIABNAE0AUwBcACIALAAgAFwAIgBrAGcAIABOAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANAAuADEALgAxAC4AMwAgACgANwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAGoAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXABuAE4AaQB0AHIAbwBnAGUAbgAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBOAFQAXwBqAG0AVAAyAFwAbgBrAGcAIABOAFwAbgBOAFQAXwB7AGoAbQAsAFQAPQAyAH0APQAoAE0ATgBfAHsAagBtAD0ANQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAHIAYQBjAEcAQQBTAE0AXwB7AG0APQA1AH0ALQBFAEYAXwB7AG0APQA1AH0AKQApAC0ATQBOAF8AewBqAG0ALABUAD0AMwB9AFwAbgBNAE4AXwBqAG0ANQBUADEAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAATQBNAFMAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBNAF8AbQA1ACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEUARgBfAG0ANQAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGQAZQBwAG8AcwBpAHQAZQBkAFwAbgBNAE4AXwBqAG0AVAAzACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAAOgAgAGsAZwAgAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBfAGoAbQA1AFQAMQAsACAARgByAGEAYwBHAEEAUwBNAF8AbQA1ACwAIABFAEYAXwBtADUALAAgAE0ATgBfAGoAbQBUADMALABcAG4AIAAgACAAIAAoAE0ATgBfAGoAbQA1AFQAMQAgACoAIAAoADEAIAAtACAARgByAGEAYwBHAEEAUwBNAF8AbQA1ACAALQAgAEUARgBfAG0ANQApACkAIAAtACAATQBOAF8AagBtAFQAMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAGcAZQBuACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBUAF8AagBtAFQAMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AVABfAHsAagBtACwAVAA9ADIAfQA9ACgATQBOAF8AewBqAG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAcgBhAGMARwBBAFMATQBfAHsAbQA9ADUAfQAtAEUARgBfAHsAbQA9ADUAfQApACkALQBNAE4AXwB7AGoAbQAsAFQAPQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AXwBqAG0ANQBUADEAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMATQBfAG0ANQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0ANQBcACIALABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAHIAeQBsAG8AdAAgAE0ATQBTAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABkAGUAcABvAHMAaQB0AGUAZABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBfAGoAbQBUADMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAE0ATQBTACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAA4ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAbgBNAE4AXwBqAG0AMQBUADMAXABuAGsAZwAgAE4AXABuAE0ATgBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBBAEUAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQA9ADEALABUAD0AMwB9AFwAbgBBAEUAXwBqACAAPQAgAHQAbwB0AGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAGIAeQAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABOAFwAbgBNAE0AUwBfAGoAbQAxAFQAMwAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBFAF8AagAsACAATQBNAFMAXwBqAG0AMQBUADMALABcAG4AIAAgACAAIABBAEUAXwBqACAAKgAgAE0ATQBTAF8AagBtADEAVAAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMwAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAF8AagBtADEAVAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAOAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE4AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AQQBFAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0APQAxACwAVAA9ADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBFAF8AagBcACIALABcACIAdABvAHQAYQBsACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAYgB5ACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwAFwAIgAsACAAXAAiAGsAZwAgAE4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA0AC4AMQAuADEALgAzACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAF8AagBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAxADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABGAGUAZQBkAGwAbwB0ACAAQgBlAGUAZgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGYAZQBlAGQAbABvAHQAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0ACAAKABkAGEAeQBzACkAXABuAE0AXwBqACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGgAZQBhAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqACAAKgAgAE4AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABEAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAXABcAHQAaQBtAGUAcwAgAE4AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ASQBfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARQBFAF8AagAgAD0AIABlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAE4ARABGAF8AagAgAD0AIABuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABFAEUAXwBqACwAIABOAEQARgBfAGoALABcAG4AIAAgACAAIAAoADUALgAxADEAIAAqACAASQBfAGoAIAAtACAANAAuADAAMAAgACoAIABFAEUAXwBqACAAKwAgADIALgAyADYAIAAqACAATgBEAEYAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGwAbQBlAGkAZABhACAAZQB0ACAAYQBsAC4AIAAoADIAMAAyADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBFAF8AagBcACIALAAgAFwAIgBlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEQARgBfAGoAXAAiACwAIABcACIAbgBlAHUAdAByAGEAbAAgAGQAZQB0AGUAcgBnAGUAbgB0ACAAZgBpAGIAcgBlACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADEAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAxAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAxAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMQBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADEAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBNAGEAbgB1AHIAZQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADkAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4AQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATQBhAG4AdQByAGUAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA5AF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBTAGMAbwBwAGUAMwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE0AYQBuAHUAcgBlAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AOQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAUwBjAG8AcABlADMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwAQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwA1AF8AXwAyAF8AVgBvAGwAYQB0AGkAbABpAHMAZQBkAE4AaQB0AHIAbwBnAGUAbgBGAHIAbwBtAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8ANQBfAF8AMgBfAFYAbwBsAGEAdABpAGwAaQBzAGUAZABOAGkAdAByAG8AZwBlAG4ARgByAG8AbQBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADUAXwBfADIAXwBWAG8AbABhAHQAaQBsAGkAcwBlAGQATgBpAHQAcgBvAGcAZQBuAEYAcgBvAG0ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABEAGkAcgBlAGMAdABOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwARABpAHIAZQBjAHQATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAEQAaQByAGUAYwB0AE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADIAXwBTAHQAYQBnAGUAMQBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEQAcgB5AGwAbwB0AF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMgBfAFMAdABhAGcAZQAxAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMARAByAHkAbABvAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAyAF8AUwB0AGEAZwBlADEATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBEAHIAeQBsAG8AdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AMwBfAEEAbgBuAHUAYQBsAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADMAXwBBAG4AbgB1AGEAbABOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwAzAF8AQQBuAG4AdQBhAGwATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADQAXwBOAGkAdAByAG8AZwBlAG4ARQB4AGMAcgBlAHQAaQBvAG4AUABlAHIASABlAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA0AF8ATgBpAHQAcgBvAGcAZQBuAEUAeABjAHIAZQB0AGkAbwBuAFAAZQByAEgAZQBhAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANABfAE4AaQB0AHIAbwBnAGUAbgBFAHgAYwByAGUAdABpAG8AbgBQAGUAcgBIAGUAYQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA1AF8ATgBpAHQAcgBvAGcAZQBuAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANQBfAE4AaQB0AHIAbwBnAGUAbgBJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADUAXwBOAGkAdAByAG8AZwBlAG4ASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANgBfAFMAdABhAGcAZQAyAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAXwBVAG4AaQB0ACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA2AF8AUwB0AGEAZwBlADIATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADYAXwBTAHQAYQBnAGUAMgBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVABpAHQAbABlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADcAXwBOAGkAdAByAG8AZwBlAG4AVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA3AF8ATgBpAHQAcgBvAGcAZQBuAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8ANwBfAE4AaQB0AHIAbwBnAGUAbgBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBNAFMAXwBGAGUAZQBkAGwAbwB0AF8ATgAyAE8ARABpAHIAZQBjAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADMAXwBfADgAXwBTAHQAYQBnAGUAMwBOAGkAdAByAG8AZwBlAG4ASQBuAE0ATQBTAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdAAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAE0AUwBfAEYAZQBlAGQAbABvAHQAXwBOADIATwBEAGkAcgBlAGMAdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMwBfAF8AOABfAFMAdABhAGcAZQAzAE4AaQB0AHIAbwBnAGUAbgBJAG4ATQBNAFMAQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0ATQBTAF8ARgBlAGUAZABsAG8AdABfAE4AMgBPAEQAaQByAGUAYwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAzAF8AXwA4AF8AUwB0AGEAZwBlADMATgBpAHQAcgBvAGcAZQBuAEkAbgBNAE0AUwBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAATQBNAFMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAG0AaQBkACAAZgBlAGQAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABsAG8AbgBnACAAZgBlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBMAGUAbgBnAHQAaAAgAG8AZgAgAFMAdABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgAxAC0AOAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgA4ADEALQAyADAAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgAyADAAMQArACAAZABhAHkAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAbQBlAGQAIAAnAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwAnACAAYwBvAGwAdQBtAG4AIAAtACAAbwByAGkAZwBpAG4AYQBsACAAaABhAHMAIABoAGUAYQBkAGUAcgAgACcAVQBuAGkAdAAnACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuACAAYwBvAGwAdQBtAG4AIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAATgBEAEYAIABhAG4AZAAgAEUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADgALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAE4AdQB0AHIAaQBlAG4AdAAgAGEAbgBhAGwAeQBzAGkAcwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADMALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADQALgA1ACwAIAA0AC4ANQAsACAANAAuADgALAAgADQALgA4ACwAIAAwAC4AMAA0ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADAALgAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4ANQAsACAANQAuADUALAAgADAALgAwADUANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAATgBTAFcAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAE4AVAAgAGMAbwBsAHUAbQBuACAAdABoAGEAdAAgAGQAdQBwAGwAaQBjAGEAdABlAHMAIABRAEwARAAgAHYAYQBsAHUAZQBzACAAYQBzACAAcABlAHIAIABhAGQAdgBpAGMAZQAgAGYAcgBvAG0AIABzAG8AdQByAGMAZQAgAGQAYQB0AGEAIABwAHIAbwB2AGkAZABlAHIALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAVABBAFMAIABjAG8AbAB1AG0AbgAgAHQAaABhAHQAIABkAHUAcABsAGkAYwBhAHQAZQBzACAAVgBJAEMAIAB2AGEAbAB1AGUAcwAgAGEAcwAgAHAAZQByACAAYQBkAHYAaQBjAGUAIABmAHIAbwBtACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAcAByAG8AdgBpAGQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFQAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMAA1ADQALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAUABvAG4AZAApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVAAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADYALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMgA1ACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgA0ACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACkAXAAiACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMQA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARgBlAGUAZABsAG8AdAAgAEIAZQBlAGYAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAxAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABmAGUAZQBkAGwAbwB0ACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABEAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAXABcAHQAaQBtAGUAcwAgAE4AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEQAXwBqACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdAAgACgAZABhAHkAcwApAFwAbgBNAF8AagAgAD0AIABkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0ACAAKABoAGUAYQBkACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAF8AagAsACAATQBfAGoALAAgAE4AXwBqACwAXABuACAAIAAgACAAKABEAF8AagAgACoAIABNAF8AagAgACoAIABOAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGYAZQBlAGQAbABvAHQAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgARABfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABOAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMQAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0AFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcAG4ATQBfAGoAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AagA9ACgANQAuADEAMQBcAFwAdABpAG0AZQBzACAASQBfAGoALQA0AC4AMAAwAFwAXAB0AGkAbQBlAHMAIABFAEUAXwBqACsAMgAuADIANgBcAFwAdABpAG0AZQBzACAATgBEAEYAXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEUARQBfAGoAIAA9ACAAZQB0AGgAZQByACAAZQB4AHQAcgBhAGMAdAAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBOAEQARgBfAGoAIAA9ACAAbgBlAHUAdAByAGEAbAAgAGQAZQB0AGUAcgBnAGUAbgB0ACAAZgBpAGIAcgBlACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAARQBFAF8AagAsACAATgBEAEYAXwBqACwAXABuACAAIAAgACAAKAA1AC4AMQAxACAAKgAgAEkAXwBqACAALQAgADQALgAwADAAIAAqACAARQBFAF8AagAgACsAIAAyAC4AMgA2ACAAKgAgAE4ARABGAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBsAG0AZQBpAGQAYQAgAGUAdAAgAGEAbAAuACAAKAAyADAAMgA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagA9ACgANQAuADEAMQBcAFwAdABpAG0AZQBzACAASQBfAGoALQA0AC4AMAAwAFwAXAB0AGkAbQBlAHMAIABFAEUAXwBqACsAMgAuADIANgBcAFwAdABpAG0AZQBzACAATgBEAEYAXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARQBfAGoAXAAiACwAIABcACIAZQB0AGgAZQByACAAZQB4AHQAcgBhAGMAdAAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBEAEYAXwBqAFwAIgAsACAAXAAiAG4AZQB1AHQAcgBhAGwAIABkAGUAdABlAHIAZwBlAG4AdAAgAGYAaQBiAHIAZQAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
+++ b/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B25205-9B25-4383-BECB-E4CCC0C3112C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA995FE-FE0E-4521-A6D8-8F4F63F29F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="780" windowWidth="37665" windowHeight="20295" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,11 +20,14 @@
     <sheet name="Input - Feedlot" sheetId="70" r:id="rId5"/>
     <sheet name="3.1.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Feedlot" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="98" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="103" r:id="rId8"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
     <sheet name="Tab template" sheetId="74" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -105,6 +108,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title">_xlfn.LAMBDA("Emission factor for organic fertiliser and crop residues returned to the soil")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
@@ -176,9 +186,12 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -190,7 +203,9 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracLEACH_MS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system","Emission factor";"Irrigated pasture",0.0059;"Irrigated crop",0.007;"Non-irrigated pasture",0.0018;"Non-irrigated crop",0.0041;"Sugar cane",0.0199;"Cotton",0.0053;"Horticulture",0.0064}, _xlpm.r, _xlpm.c))))</definedName>
@@ -358,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
   <si>
     <t>Home</t>
   </si>
@@ -1034,6 +1049,12 @@
   </si>
   <si>
     <t>Input - Feedlot</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>EFNi &amp; EFN2Oi</t>
   </si>
 </sst>
 </file>
@@ -2380,7 +2401,31 @@
     <cellStyle name="Variable type input" xfId="64" xr:uid="{515940C5-98BF-44F7-AAB8-0D7808DD5C6C}"/>
     <cellStyle name="Variable type other" xfId="65" xr:uid="{5D88A237-9D54-45E0-A48E-F67D0639FDE2}"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4097,20 +4142,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="74"/>
-      <tableStyleElement type="headerRow" dxfId="73"/>
-      <tableStyleElement type="totalRow" dxfId="72"/>
-      <tableStyleElement type="firstColumn" dxfId="71"/>
-      <tableStyleElement type="firstRowStripe" dxfId="70"/>
-      <tableStyleElement type="secondRowStripe" dxfId="69"/>
+      <tableStyleElement type="wholeTable" dxfId="75"/>
+      <tableStyleElement type="headerRow" dxfId="74"/>
+      <tableStyleElement type="totalRow" dxfId="73"/>
+      <tableStyleElement type="firstColumn" dxfId="72"/>
+      <tableStyleElement type="firstRowStripe" dxfId="71"/>
+      <tableStyleElement type="secondRowStripe" dxfId="70"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="68"/>
-      <tableStyleElement type="headerRow" dxfId="67"/>
-      <tableStyleElement type="totalRow" dxfId="66"/>
-      <tableStyleElement type="firstColumn" dxfId="65"/>
-      <tableStyleElement type="firstRowStripe" dxfId="64"/>
-      <tableStyleElement type="secondRowStripe" dxfId="63"/>
+      <tableStyleElement type="wholeTable" dxfId="69"/>
+      <tableStyleElement type="headerRow" dxfId="68"/>
+      <tableStyleElement type="totalRow" dxfId="67"/>
+      <tableStyleElement type="firstColumn" dxfId="66"/>
+      <tableStyleElement type="firstRowStripe" dxfId="65"/>
+      <tableStyleElement type="secondRowStripe" dxfId="64"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -5778,6 +5823,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5861,34 +5926,34 @@
     <tableColumn id="1" xr3:uid="{3885FE93-299E-44EB-B503-99C305BD6F41}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D0E12F95-AC29-47D0-913A-0A0B02931616}" name="MMS m" dataDxfId="62" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D0E12F95-AC29-47D0-913A-0A0B02931616}" name="MMS m" dataDxfId="63" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E17BE7AB-8FAD-4B5C-9F86-E70E6A00B9B1}" name="NSW" dataDxfId="61" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E17BE7AB-8FAD-4B5C-9F86-E70E6A00B9B1}" name="NSW" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D4C6F922-2719-4479-B7CC-26C5286F73ED}" name="ACT" dataDxfId="60" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D4C6F922-2719-4479-B7CC-26C5286F73ED}" name="ACT" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="59" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5034DCA1-F046-43BC-A94F-832832E6D634}" name="QLD" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{186521AB-DFC2-4E3B-A674-A5382DCC5ACD}" name="NT" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{95F9E197-F85F-424A-B68D-774604116729}" name="SA" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{A6DDF652-660B-4C41-982D-FECC3B1142AF}" name="VIC" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{5163E1D2-D984-4DBA-95A9-1667F628B2D9}" name="WA" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A0E67108-978C-4849-A310-69F8E4739C6D}" name="TAS" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{27E929DD-0554-43B8-A58C-34B0A39F2EBA}" name="NIR definition" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_MCF_Data(), Table_SourceData_Feedlot_MCF[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5897,20 +5962,20 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{819F82E1-8BFB-49BB-A84C-1541D2694B39}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6DA59241-5AD2-4A3A-9CCD-E44D4FDB051A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{70652AFC-F3E8-4421-AFD1-2D686D40D22D}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{3C89B748-4AE6-4C8B-B1C9-14C972049D59}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1FA7E548-C0EA-432C-8E8B-704642D10B8B}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{8C647A29-9B6F-4936-A84C-DC5513ED1544}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EBC3E112-1444-44E8-96B3-3CA9BA6303FD}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{06210813-CC74-4796-BBCB-D954DE0AF99B}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5919,12 +5984,12 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4E187021-E65C-4405-B076-51664A260F70}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A2E539BE-7696-4F96-BE6D-ECC6852634D6}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{BE8A74F0-502F-4C09-B30D-79967B1CA4B3}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{90CD384E-DB1E-4D14-912E-34F82AB7435A}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5933,16 +5998,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{E185DEA7-0F0B-4043-8184-02AAE04CE1D3}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{52069AD2-EB42-429E-AEB3-CEF981561E89}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{969FB6F5-5748-416A-B0E7-0FA856E9228D}" name="Gas">
+    <tableColumn id="1" xr3:uid="{8D754EBA-F415-4A61-AA0C-4A36E97D77F8}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D288383E-5A93-48FA-8608-CEA132940F23}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{A35F7B27-4598-41B9-B2AF-E891DD177E4F}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5951,7 +6016,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{FC1E3F9B-244C-4BDB-9EAA-280B1B88DFD0}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{E4B112D2-CF95-44F4-A335-28B651D2B863}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5960,19 +6025,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9107412D-787D-4251-B022-2C951856B5CC}" name="Gas">
+    <tableColumn id="1" xr3:uid="{E69A30C0-22D5-4BA8-AFDB-76AA923C8527}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EDAE218C-BED9-4F30-BC1A-BDA604C52911}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{DAB01283-FC71-431B-A277-484BFD2852AE}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7B252330-4D09-4BE1-91E1-8F007E37DA8F}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{7CE86A10-8384-4E44-AC14-3D195943287A}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EB2A94A6-B09F-44FC-92A1-CCB07CD838C7}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{3DA6B978-29FB-4351-B0B5-A90C0833A1E6}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F2DB3A9E-EA47-4626-8AA6-4142F2BE5B34}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{C4B32275-A174-4646-8545-FE922F2AA4E4}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5981,7 +6046,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EC639B46-F2B6-417E-849A-4051D3B16B01}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{32EBF617-0335-41AA-ADB7-3EBAFDF1CC1A}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6001,52 +6066,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{25162FA7-7F7F-4C9C-8231-8FC51C581FD1}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C4862F40-DA25-46E8-8D76-48B467179FB5}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E2C0A27-43A1-4D92-B3A8-944DC7691E0A}" name="MAT" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{3C70C8C5-2E57-4167-9586-23EBEC647C48}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BCEE406F-741C-4AB5-8347-FD3CEB5D1690}" name="MAP" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{7BD37B7B-611E-4693-B085-60B9F9FC0CC9}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BF112A88-84E8-4D38-B54C-79713ED69470}" name="Frost days per year" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{EE14D82D-9AEA-416C-AFA4-10C9AD5E726D}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DEDF2179-1AFD-46AA-97FF-2C7CC2C8F0A0}" name="Elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{3C1E1023-EFDB-49D3-BAE9-1B1BF3C98BCC}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{517703E3-C0ED-43E3-909F-4C1979577D3C}" name="MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{A2CA66E0-E9CC-421A-BB3C-AA60A9404533}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{666A24A7-650A-4B3E-982A-50311730DB7C}" name="Min temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{31D6DD62-0E13-4C4A-9480-269DC4FA9BB0}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5604EDD5-66DF-4ECC-BCE6-DD11FD6DB4D6}" name="Max temp" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{E033E4FF-C946-4A06-B69D-E49EA6CF9BAA}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6DA99F2D-CE18-432C-AB0D-72F425C17C5E}" name="Min rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{A579442E-001E-4C0D-9ED3-546DD4A71B1D}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BC2916D3-A7D1-4722-A9DC-991CB2F62BD8}" name="Max rainfall" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{D0EFE677-4876-48CD-BECC-65303AEB1FC3}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1E64F234-4E02-4B45-A3A1-B18E3FFCFC37}" name="Min frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{BDDC01FF-4C94-4D2B-8A29-9A6A182D577A}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{70F03B18-1155-4824-8E62-AE5F3FA2A39C}" name="Max frost days" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{32E45C95-F46C-4789-9501-1354CF9F81F2}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C3AD9C66-0836-47F7-A64C-E903E6DAF5EE}" name="Min elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{D218B674-8D34-44E2-81A3-629AC0DE1D2F}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{ED33ED06-8D20-47FE-B0B6-650FCDD420E2}" name="Max elevation" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{1CF5EDC4-DC46-40C6-890D-16AEE56DB611}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3C28BB66-16DC-4BC9-BE53-61187001ECC2}" name="Min MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{A605A890-95A1-46E3-BE8F-B52A62F73CC0}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{FFF015AD-8516-434B-A94C-11CB9D62F62D}" name="Max MAP:PET" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{BB0D236B-CA39-4D1A-BEE8-8F84BD3C9958}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6055,16 +6120,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B975CFAC-C9D3-4E10-914B-A74776502697}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{9BCA601F-C8EB-4CFB-9149-6F11DBF54AAE}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2BBE1D44-5D3C-421E-B886-5F058BD82B23}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{B9BAA817-17FD-4F01-8106-570A360D8738}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C3E0B2F3-1F7B-4FCF-B0F4-658087312975}" name="Wet or Dry Zone" totalsRowDxfId="19" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6395ED2C-7F36-4012-8B9E-202C1745C29C}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6073,7 +6138,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{4F86B9BF-70ED-46B9-A712-EA42AC73454A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{AC94864B-F189-44AA-BB3A-361B961FDF2F}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6081,16 +6146,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D5BB3355-DBBC-43C3-9C8D-BC097471993C}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{DD345E07-61B9-41DB-B5BA-DB28FAD4A161}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{15DB6AA7-91D7-4725-9AA9-D1055AF7678C}" name="MAT">
+    <tableColumn id="2" xr3:uid="{A711C554-6BE8-4AE4-B966-ECD763ACD646}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0AD7766B-F917-4247-BA12-141E5E455D92}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{3984F636-29BC-4CE5-8CF3-2329A9C2A7D2}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEC491C5-29B7-47D8-92E3-A6B4AA3DF904}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{3FCCC739-2922-4D2F-9DC0-3537F0E5977F}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6099,7 +6164,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{FF94A906-91DA-4FAF-A89B-CEF60B0D1275}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{347ABED6-2FC5-417A-9FCD-CB8FFE53FE87}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6107,16 +6172,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3D6E0C09-0BD8-471F-8A53-A12A9E178BF7}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{8146FC52-A477-4479-8B4B-720456989392}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{13B32985-837D-4685-9D0B-839BCC352710}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{FD0BC088-CB5A-442E-ACFF-6575CD9C3F67}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{81010191-F2A6-4E17-8104-721B45E9D660}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{C1533A8E-00D9-48AA-BF77-E4DF9ED68F7A}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AD6D3163-2840-4E3F-896D-5DF709C34D97}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{D905FCD2-CEB1-4711-A8AA-0770FBC8592D}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6125,16 +6190,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{1A2C3C00-7D5E-482F-8CA2-A213D7DF8D38}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{95724543-CBBD-43C1-8D9F-8670C8AF5EC7}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A4167ABF-B475-4336-9AEE-96008ED98E6B}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{807F0A0D-7729-434A-B81A-37C27B571F26}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{75B56258-627E-484F-9B94-6FD90490B5C5}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{509072A7-1958-4360-8769-DDC75F87F211}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6143,16 +6208,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4B10AEB1-ABAB-4497-8F48-0C15CDA46026}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C812ED3C-8F80-4D22-B6D4-AC035CC2B4D5}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{48FCAEBE-8FA0-4664-B3AE-973A3E77EF02}" name="Data source">
+    <tableColumn id="1" xr3:uid="{B4613496-7E6F-4194-A901-FC86EBBADB33}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F269D724-DA61-40DD-B1DD-62089B53A254}" name="Data score">
+    <tableColumn id="2" xr3:uid="{28219049-A63B-47B1-A48A-916BA0692C82}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6168,23 +6233,23 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="52" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="53" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{45FE08A5-0001-4080-8F90-757F959BAB2B}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{655CCD8B-BF0E-4948-A8C5-EE60DFE71239}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ACC4E2B3-A6FC-4D50-BE90-6D711BFC3B97}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{36433F79-A4C4-4EB6-BD10-D67BAF3D7A0D}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{35F8284C-32FA-4320-AF32-3F44CCB77CF7}" name="FracWET" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{A1C64A0B-5195-428F-B6F5-8C546D8B057A}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6193,7 +6258,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{B985452B-55AC-4EB5-AA25-EAD220463DA8}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{8933C84F-E844-4CD7-A925-692935723E8F}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6202,19 +6267,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D74A144B-9F75-433D-BE41-D183AF51F2BB}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{82A5C969-9C3F-4F73-AC8B-C639D2BDBFB4}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{87B0476D-5F45-43A5-9823-48327AFBBFC0}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{AB9501BB-2639-43D6-B68A-79294194505F}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A580C8EE-E9FD-4201-94D1-F99A9BC27373}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{EFCB2B6D-DE4F-482C-9387-9E8A91B5B8CF}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{50C2C17E-A21C-4FDA-82A8-EF761C0E6BF7}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{81CE6B4D-17AF-41CF-870D-18D8DAF3CABC}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7F2E249C-6080-446E-8674-6F29CE0873E0}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{18FB9AB9-FDC3-41EA-AC43-6A6CBBE82ED1}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6223,16 +6288,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{F1D7CB04-0839-425A-B673-CEA7A9C3FB85}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F47688AB-E0DE-4988-999F-8F08D3561244}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6328C683-420D-4EA6-AF9D-245995DC8FD1}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{21589287-984E-48C4-943A-79545E6B174C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E5FEA9D-8FB5-494C-9D24-0E6BFC0C6057}" name="FracWET" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8E9CDD17-EE99-4778-B09F-4E0C2FB99750}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6241,16 +6306,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{E9AFCB04-6C42-4BD7-84F4-CB502355AF0E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{158328B6-3907-4392-AFC2-F8C4AB7BBB98}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FB787692-FEAA-422C-9A68-A116E1C1D839}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{6A2682B4-C3D3-41B1-A9A5-CD341B338AD2}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFBB6C89-F456-4C86-80FD-B734DEFDFF30}" name="EFPRP" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A75E28E6-0789-4F0F-81F1-A24152E59D86}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6259,16 +6324,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{A23F6973-616E-44B9-9455-AEC834A8AADB}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{B7245AEF-8BAD-4F83-B5FE-FA6C33BBCD26}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E0DBFFCC-335E-4C29-BC47-5C2A3243CFF0}" name="Month">
+    <tableColumn id="1" xr3:uid="{B7F13D52-90A1-46F1-AE87-C3A50775031E}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AC3827EF-FE9E-4E81-A7C7-95A7165D62C5}" name="Season" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{18651875-AACE-4C83-82EC-A3F943EFB45C}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6277,7 +6342,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{88FD98D7-E5DB-4B28-9E47-A6481BEC1373}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{E69BCEBA-1BD2-41DB-BC12-595C5098C6D6}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6297,52 +6362,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8C0CBC0D-B831-4C7E-9F24-0EE0037F3E6B}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{A24B9C52-FFAF-493E-B255-DF0C055293B7}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B6E0D171-2FBE-46A9-9B1F-1269E55C1B38}" name="MAT (ºC)" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1B432806-D53F-4B46-A933-51812CFD4E94}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7FF50BBA-30EE-4E1A-9449-9265A1067683}" name="Anaerobic lagoon" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{64223CF6-132B-4BB5-935D-463ED805DB6A}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{53654E61-5BB1-44D1-A97F-E38B4117F28F}" name="Digester / covered lagoons" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{398F74B0-242B-4BDB-8BE1-EA23C634046B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5736C277-B619-4577-BE61-C6F2CFEBBDF4}" name="Liquid systems" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{085C948A-B26D-4F7E-A0BA-D25E0DF8A9C9}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A4F5FCA7-77C5-40B2-BAC9-EBF849F5559B}" name="Daily spread" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{41D49491-8B7C-4AB1-95F1-B26E9D3666B4}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D7CABD47-531A-49AF-865F-934434068DEC}" name="Composting (passive windrow)" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{58B38240-35E8-4B61-8CAD-C0D8945722E2}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5B3C335A-BC58-40E9-8E75-96ED6CCF795D}" name="Solid storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{B02EF87A-9257-4105-9F8A-B8398BA5C272}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2D3901FD-AFED-45CA-9E32-1204AF6D4874}" name="Pit storage" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{06C3FA49-4472-45AF-B982-255330DAAF3F}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{343A0FE7-0AA0-43C9-9A4F-02E9C242020A}" name="Deep litter" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{50E31972-10A3-458E-99D9-A6039185A4C0}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FAF69A1E-4587-4DCD-9535-2ECADB3A8A73}" name="Poultry manure with bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{4FEDC0E7-4585-41D0-9D82-E51CFC16C0AC}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9D86AF5D-FDC1-4EE1-9D47-BA4BE96F619F}" name="Poultry manure without bedding" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{4813997B-550E-4DCE-87B4-80A682C2C0DA}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C15483D8-6A7E-4D26-B81F-096629F52A98}" name="Direct processing" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{F2E360E2-34AD-40DB-93A5-5722025EE092}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F82A14FE-E6A5-4C72-AE16-87CCAF66B3DB}" name="Direct application" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{34798E98-3096-45B5-9CD9-6F2AA46F54F2}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{DBBFE03E-A035-4E39-B68B-F044C4B1E37F}" name="Pasture range and paddock" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{C707BBDE-FE68-40C0-8AEC-7E0767B66EEF}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{EE478F66-8602-4161-AB22-52FED9A026F5}" name="MAT raw" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{44DE0740-88AE-4422-B380-25FA55DF3ABD}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6351,6 +6416,24 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{857070AE-A158-45E7-B88D-BD25C5BAF14F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{16E298C9-BE0C-4CA4-9612-B74156CF176F}" name="Climate Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{7D2C8B74-D5CB-41CE-BE7A-63ACA70B1F30}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D9:F27" totalsRowShown="0">
   <autoFilter ref="D9:F27" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6387,22 +6470,22 @@
     <tableColumn id="1" xr3:uid="{FDCB848C-205F-48EA-BACF-F54BCD324E05}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3306F917-B06C-4CC9-B1B1-D97D858E6DAA}" name="Nutrient analysis" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{F162F7C2-B0FA-499A-BD58-855C4DF97FA8}" name="Unit" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{D395A9F5-9A85-4032-A7C1-EC470516DD87}" name="2010-2014" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{B149E561-7044-4839-B850-C751ABC364C9}" name="2015-2019" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{ECEB8E53-4880-43AE-9D36-F969D05BCB18}" name="2020-2023" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3B7FAEA4-08D7-48B2-9062-7D93639222CC}" name="2020-2023 Converted to fraction" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data(), Table_SourceData_Feedlot_DietProperties[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6425,22 +6508,22 @@
     <tableColumn id="1" xr3:uid="{96F6B4E3-E1EE-445F-9BCE-628B89FC3727}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6B651FD0-BCF6-4081-8A93-6B21A1D6CA99}" name="Characteristic" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F266A2B-76EA-4E95-B049-75B8E4AB351F}" name="Unit" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{15472767-3F72-4A65-88AC-C3242A8E1662}" name="2005-2009" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{5F74A8B9-7EFB-4457-8ADA-5E1ABA9DA889}" name="2010-2014" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E54F2812-2E8B-41EB-98A8-46890B5B4E13}" name="2015-2019" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{88EEE0E3-F5D0-41DF-80EF-59472377C29A}" name="2020-2023" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data(), Table_SourceData_Feedlot_AnimalCharacteristics[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6458,7 +6541,7 @@
     <tableColumn id="1" xr3:uid="{9D472457-4D8B-44ED-9567-B889D058C2F1}" name="Feedlot type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DA3DA009-634B-4C70-926B-C8FB255EB4DC}" name="Length of stay" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_DurationOfStay_Data(), Table_SourceData_Feedlot_LengthOfStay[[#Headers],[Feedlot type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6478,13 +6561,13 @@
     <tableColumn id="1" xr3:uid="{C80C08D8-3F48-4E18-98E3-9B53ACB6C6D9}" name="Treatment stage T">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2BCD8589-5CB8-4ED1-AF2B-2866CEF779A8}" name="MMS m" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{51E876CD-83B6-49C8-85DD-E2F427A3DCD0}" name="EF mT" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{BEDEE6BB-8013-495A-8D74-2C8D37558C98}" name="NIR definition" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Feedlot.SourceData_Feedlot_NitrousOxideEFs_Data(), Table_SourceData_Feedlot_NO2EFs[[#Headers],[Treatment stage T]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6493,7 +6576,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}" name="Table_SourceData_Feedlot_FracGASMmT" displayName="Table_SourceData_Feedlot_FracGASMmT" ref="D112:G117" totalsRowShown="0" headerRowDxfId="36" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D112:G117" xr:uid="{100A8309-C0D3-4638-A47B-72840A042D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -18385,8 +18468,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7548F5C8-4326-4B87-AF98-B62783E0FF5C}">
-  <dimension ref="A1:BY250"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6290569-6D3E-4A60-8159-28E6A69C4E62}">
+  <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
@@ -19789,31 +19872,31 @@
       </c>
       <c r="T97" s="37"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="52" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="52" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="52" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="52" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="52" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="52" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="52"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="52"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
@@ -22299,10 +22382,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D253" s="6" t="str" cm="1">
+        <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
+        <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
+      </c>
+    </row>
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D254" s="5" t="str" cm="1">
+        <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
+        <v>VEERG 2026: Table A.2.1.4</v>
+      </c>
+    </row>
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D255" s="1" t="str" cm="1">
+        <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
+        <v>EFNi &amp; EFN2Oi</v>
+      </c>
+    </row>
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D256" s="52" t="str" cm="1">
+        <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E257" s="37" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" s="37" t="str" cm="1">
+        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E258" s="37" cm="1">
+        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="1" t="str" cm="1">
+        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E259" s="37" cm="1">
+        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="16">
+  <tableParts count="17">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -22319,6 +22454,7 @@
     <tablePart r:id="rId15"/>
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -22801,17 +22937,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAATQBNAFMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAG0AaQBkACAAZgBlAGQAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABsAG8AbgBnACAAZgBlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBMAGUAbgBnAHQAaAAgAG8AZgAgAFMAdABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgAxAC0AOAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgA4ADEALQAyADAAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgAyADAAMQArACAAZABhAHkAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAbQBlAGQAIABcAHUAMAAwADIANwBjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAC0AIABvAHIAaQBnAGkAbgBhAGwAIABoAGEAcwAgAGgAZQBhAGQAZQByACAAXAB1ADAAMAAyADcAVQBuAGkAdABcAHUAMAAwADIANwAgAHcAaABpAGMAaAAgAGMAbwB2AGUAcgBzACAAdAB3AG8AIABjAG8AbAB1AG0AbgBzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAANwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAANwAwACwAIAA3ADAALAAgADcAMAAsACAANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADAALgAwACwAIAAxADAALgAwACwAIAAxADAALgA0ACwAIAAxADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAyADEALgAxACwAIAAyADAALgA0ACwAIAAyADAALgA0ACwAIAAyADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADEAMQA1ACwAIAAxADEANQAsACAAMQAyADAALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAxAC4AMgAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADEAMgAuADUALAAgADEAMgAuADcALAAgADEAMgAuADcALAAgADEAMgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAOQAuADAALAAgADgALgA1ACwAIAA4AC4AMgAsACAAOAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADYALgA2ACwAIAA3AC4AMAAsACAANwAuADAALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQwBvAG4AdgBlAHIAdABlAGQAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AIABjAG8AbAB1AG0AbgAgAGEAbgBkACAAYwBvAG4AdgBlAHIAdABlAGQAIABOAEQARgAgAGEAbgBkACAARQB0AGgAZQByACAAZQB4AHQAcgBhAGMAdAAgAHYAYQBsAHUAZQBzACAAdABvACAAZgByAGEAYwB0AGkAbwBuAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAOAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATgB1AHQAcgBpAGUAbgB0ACAAYQBuAGEAbAB5AHMAaQBzAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAdABlAGQAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgAxADQALAAgADAALgAxADQALAAgADAALgAxADQALAAgADAALgAxADQALAAgADAALgAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIAMwAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADAALgAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANAAuADUALAAgADQALgA1ACwAIAA0AC4AOAAsACAANAAuADgALAAgADAALgAwADQAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgAxADMALAAgADAALgAxADIANQAsACAAMAAuADEAMgAsACAAMAAuADEAMgAsACAAMAAuADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADAALgAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgAxADMALAAgADAALgAxADIANQAsACAAMAAuADEAMgAsACAAMAAuADEAMgAsACAAMAAuADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgA0AC4AMAAsACAAMgA0AC4AMAAsACAAMgA0AC4AMAAsACAAMAAuADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgA1ACwAIAA1AC4ANQAsACAAMAAuADAANQA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAE0AQwBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABOAFMAVwAgAHYAYQBsAHUAZQBzACAAZgBvAHIAIABBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAATgBUACAAYwBvAGwAdQBtAG4AIAB0AGgAYQB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAgAFEATABEACAAdgBhAGwAdQBlAHMAIABhAHMAIABwAGUAcgAgAGEAZAB2AGkAYwBlACAAZgByAG8AbQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHAAcgBvAHYAaQBkAGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABUAEEAUwAgAGMAbwBsAHUAbQBuACAAdABoAGEAdAAgAGQAdQBwAGwAaQBjAGEAdABlAHMAIABWAEkAQwAgAHYAYQBsAHUAZQBzACAAYQBzACAAcABlAHIAIABhAGQAdgBpAGMAZQAgAGYAcgBvAG0AIABzAG8AdQByAGMAZQAgAGQAYQB0AGEAIABwAHIAbwB2AGkAZABlAHIALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFQAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMAA1ADQALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAUABvAG4AZAApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4ANgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADQALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAxADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABGAGUAZQBkAGwAbwB0ACAAQgBlAGUAZgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGYAZQBlAGQAbABvAHQAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0ACAAKABkAGEAeQBzACkAXABuAE0AXwBqACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGgAZQBhAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqACAAKgAgAE4AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABEAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAXABcAHQAaQBtAGUAcwAgAE4AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ASQBfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARQBFAF8AagAgAD0AIABlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAE4ARABGAF8AagAgAD0AIABuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABFAEUAXwBqACwAIABOAEQARgBfAGoALABcAG4AIAAgACAAIAAoADUALgAxADEAIAAqACAASQBfAGoAIAAtACAANAAuADAAMAAgACoAIABFAEUAXwBqACAAKwAgADIALgAyADYAIAAqACAATgBEAEYAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGwAbQBlAGkAZABhACAAZQB0ACAAYQBsAC4AIAAoADIAMAAyADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBFAF8AagBcACIALAAgAFwAIgBlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEQARgBfAGoAXAAiACwAIABcACIAbgBlAHUAdAByAGEAbAAgAGQAZQB0AGUAcgBnAGUAbgB0ACAAZgBpAGIAcgBlACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -23006,31 +23144,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAATQBNAFMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAG0AaQBkACAAZgBlAGQAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABsAG8AbgBnACAAZgBlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBMAGUAbgBnAHQAaAAgAG8AZgAgAFMAdABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgAxAC0AOAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgA4ADEALQAyADAAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgAyADAAMQArACAAZABhAHkAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAbQBlAGQAIAAnAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwAnACAAYwBvAGwAdQBtAG4AIAAtACAAbwByAGkAZwBpAG4AYQBsACAAaABhAHMAIABoAGUAYQBkAGUAcgAgACcAVQBuAGkAdAAnACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuACAAYwBvAGwAdQBtAG4AIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAATgBEAEYAIABhAG4AZAAgAEUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADgALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAE4AdQB0AHIAaQBlAG4AdAAgAGEAbgBhAGwAeQBzAGkAcwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADMALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADQALgA1ACwAIAA0AC4ANQAsACAANAAuADgALAAgADQALgA4ACwAIAAwAC4AMAA0ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADAALgAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4ANQAsACAANQAuADUALAAgADAALgAwADUANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAATgBTAFcAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAE4AVAAgAGMAbwBsAHUAbQBuACAAdABoAGEAdAAgAGQAdQBwAGwAaQBjAGEAdABlAHMAIABRAEwARAAgAHYAYQBsAHUAZQBzACAAYQBzACAAcABlAHIAIABhAGQAdgBpAGMAZQAgAGYAcgBvAG0AIABzAG8AdQByAGMAZQAgAGQAYQB0AGEAIABwAHIAbwB2AGkAZABlAHIALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAVABBAFMAIABjAG8AbAB1AG0AbgAgAHQAaABhAHQAIABkAHUAcABsAGkAYwBhAHQAZQBzACAAVgBJAEMAIAB2AGEAbAB1AGUAcwAgAGEAcwAgAHAAZQByACAAYQBkAHYAaQBjAGUAIABmAHIAbwBtACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAcAByAG8AdgBpAGQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFQAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMAA1ADQALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAUABvAG4AZAApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AVAAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADYALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMgA1ACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAUABhAHMAcwBpAHYAZQAgAFcAaQBuAGQAcgBvAHcAKQBcACIALAAgADAALgA0ACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACkAXAAiACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMQA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARgBlAGUAZABsAG8AdAAgAEIAZQBlAGYAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAxAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABmAGUAZQBkAGwAbwB0ACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAbgBFAF8AZQBuAHQAZQByAGkAYwBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABEAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAXABcAHQAaQBtAGUAcwAgAE4AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEQAXwBqACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdAAgACgAZABhAHkAcwApAFwAbgBNAF8AagAgAD0AIABkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0ACAAKABoAGUAYQBkACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAF8AagAsACAATQBfAGoALAAgAE4AXwBqACwAXABuACAAIAAgACAAKABEAF8AagAgACoAIABNAF8AagAgACoAIABOAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGYAZQBlAGQAbABvAHQAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgARABfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABOAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAXAAiACwAIABcACIAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMQAuADEALgAxACwAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGoAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0AFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcAG4ATQBfAGoAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AagA9ACgANQAuADEAMQBcAFwAdABpAG0AZQBzACAASQBfAGoALQA0AC4AMAAwAFwAXAB0AGkAbQBlAHMAIABFAEUAXwBqACsAMgAuADIANgBcAFwAdABpAG0AZQBzACAATgBEAEYAXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEUARQBfAGoAIAA9ACAAZQB0AGgAZQByACAAZQB4AHQAcgBhAGMAdAAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBOAEQARgBfAGoAIAA9ACAAbgBlAHUAdAByAGEAbAAgAGQAZQB0AGUAcgBnAGUAbgB0ACAAZgBpAGIAcgBlACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsACAARQBFAF8AagAsACAATgBEAEYAXwBqACwAXABuACAAIAAgACAAKAA1AC4AMQAxACAAKgAgAEkAXwBqACAALQAgADQALgAwADAAIAAqACAARQBFAF8AagAgACsAIAAyAC4AMgA2ACAAKgAgAE4ARABGAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBsAG0AZQBpAGQAYQAgAGUAdAAgAGEAbAAuACAAKAAyADAAMgA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagA9ACgANQAuADEAMQBcAFwAdABpAG0AZQBzACAASQBfAGoALQA0AC4AMAAwAFwAXAB0AGkAbQBlAHMAIABFAEUAXwBqACsAMgAuADIANgBcAFwAdABpAG0AZQBzACAATgBEAEYAXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARQBfAGoAXAAiACwAIABcACIAZQB0AGgAZQByACAAZQB4AHQAcgBhAGMAdAAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBEAEYAXwBqAFwAIgAsACAAXAAiAG4AZQB1AHQAcgBhAGwAIABkAGUAdABlAHIAZwBlAG4AdAAgAGYAaQBiAHIAZQAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23049,18 +23190,13 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
+++ b/Excel/3_1_Enteric_Feedlot_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA995FE-FE0E-4521-A6D8-8F4F63F29F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29D578C-F500-4437-9BEB-9407CFE8A088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Input - Feedlot" sheetId="70" r:id="rId5"/>
     <sheet name="3.1.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Feedlot" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="103" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="104" r:id="rId8"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
     <sheet name="Tab template" sheetId="74" r:id="rId11"/>
@@ -5962,20 +5962,20 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6DA59241-5AD2-4A3A-9CCD-E44D4FDB051A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7160F4D5-69C3-498B-8768-94305C20B0A7}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C89B748-4AE6-4C8B-B1C9-14C972049D59}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{51475CB9-98D1-4367-81FE-766354D03859}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8C647A29-9B6F-4936-A84C-DC5513ED1544}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{E5F4A4C1-F79D-42CE-8C7B-73B43952AF82}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{06210813-CC74-4796-BBCB-D954DE0AF99B}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{1ED2BE90-6504-4529-96D4-F2168C2206DB}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5984,12 +5984,12 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A2E539BE-7696-4F96-BE6D-ECC6852634D6}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AE790257-56EE-4D3A-9E9F-63BBBD489E9B}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{90CD384E-DB1E-4D14-912E-34F82AB7435A}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{4834DA3C-E2C6-46A6-8B67-669901690AE1}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5998,16 +5998,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{52069AD2-EB42-429E-AEB3-CEF981561E89}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C748BD76-E957-4735-8DCC-4AA536F7251B}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8D754EBA-F415-4A61-AA0C-4A36E97D77F8}" name="Gas">
+    <tableColumn id="1" xr3:uid="{BC533CA1-A19D-4D88-851F-C6B55789EEF0}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A35F7B27-4598-41B9-B2AF-E891DD177E4F}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{0744ED04-F9F9-4292-9C48-DCEC4CDB7B4B}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6016,7 +6016,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{E4B112D2-CF95-44F4-A335-28B651D2B863}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4DA84FD9-456A-4D76-8824-68BDCA1A0242}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6025,19 +6025,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E69A30C0-22D5-4BA8-AFDB-76AA923C8527}" name="Gas">
+    <tableColumn id="1" xr3:uid="{DE8A5F5D-380F-444B-895F-03A04F993303}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DAB01283-FC71-431B-A277-484BFD2852AE}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{04DD10EA-0C74-4AE3-847F-091B6E17E288}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7CE86A10-8384-4E44-AC14-3D195943287A}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{B3B93DCD-8572-498D-8FD9-DE5161A70238}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3DA6B978-29FB-4351-B0B5-A90C0833A1E6}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{4AEFFF08-7C7F-45E3-BC84-7908AF11C801}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C4B32275-A174-4646-8545-FE922F2AA4E4}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{C1AE1CC4-4B45-4D28-ACD1-DCB5A0BDE3F5}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6046,7 +6046,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{32EBF617-0335-41AA-ADB7-3EBAFDF1CC1A}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{FE2FCFF0-2F5D-46AD-A562-2B5CA89C224F}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6066,52 +6066,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C4862F40-DA25-46E8-8D76-48B467179FB5}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{BB64EF18-D941-4F52-A1B2-667BE97CB825}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3C70C8C5-2E57-4167-9586-23EBEC647C48}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{98934DD4-8710-4F12-95E3-FF8487499DD5}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7BD37B7B-611E-4693-B085-60B9F9FC0CC9}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{06CB93CF-EB6F-4172-85A6-ABDCD87EBE4A}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EE14D82D-9AEA-416C-AFA4-10C9AD5E726D}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{9031FFF8-3C81-4F0A-BD57-02808D6AA1A2}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3C1E1023-EFDB-49D3-BAE9-1B1BF3C98BCC}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{BEBBB14D-687E-40D7-8A5C-830F1BF21708}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A2CA66E0-E9CC-421A-BB3C-AA60A9404533}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{59D992F0-26FC-4409-8EFD-219C6E95F62E}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{31D6DD62-0E13-4C4A-9480-269DC4FA9BB0}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{9E1C5BA7-00D4-456C-BD35-A1A477A849E3}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E033E4FF-C946-4A06-B69D-E49EA6CF9BAA}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B7E08E46-7D40-4A1B-85A5-2CBC68950E27}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A579442E-001E-4C0D-9ED3-546DD4A71B1D}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{8DB33ADB-7FE8-4683-A42A-7B517C31FB73}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{D0EFE677-4876-48CD-BECC-65303AEB1FC3}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{66872F0F-8733-4F0D-BAA4-7FB3E232EC5B}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BDDC01FF-4C94-4D2B-8A29-9A6A182D577A}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{5BE2D3A3-9488-4CDA-A5C9-C914DE17BBDA}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{32E45C95-F46C-4789-9501-1354CF9F81F2}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{87A2B35F-81EF-49FE-8E1C-DF65C2C68825}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D218B674-8D34-44E2-81A3-629AC0DE1D2F}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{511CC549-5A99-4B0F-A28E-3A5AB574B811}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1CF5EDC4-DC46-40C6-890D-16AEE56DB611}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{9C4D55D3-27D4-4F56-AA8B-6A3586706EBF}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A605A890-95A1-46E3-BE8F-B52A62F73CC0}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{96690360-D247-477E-86B7-F95A760E53DE}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{BB0D236B-CA39-4D1A-BEE8-8F84BD3C9958}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{ADA6D733-164A-4027-9A96-8515CB5C69FD}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6120,16 +6120,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{9BCA601F-C8EB-4CFB-9149-6F11DBF54AAE}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{84F274C9-B9BB-4501-85EC-CEB9C416829E}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B9BAA817-17FD-4F01-8106-570A360D8738}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{AD84D891-CBE0-4BBE-A645-C24CA6B914EA}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6395ED2C-7F36-4012-8B9E-202C1745C29C}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{BF4189CF-7E91-483C-B1DA-119B7CA28079}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6138,7 +6138,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{AC94864B-F189-44AA-BB3A-361B961FDF2F}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{C652E3F2-AB22-4ACF-92AA-A6AEB37E80BD}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6146,16 +6146,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DD345E07-61B9-41DB-B5BA-DB28FAD4A161}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{C3C0E923-E589-4E34-8701-DB8EC6258A11}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A711C554-6BE8-4AE4-B966-ECD763ACD646}" name="MAT">
+    <tableColumn id="2" xr3:uid="{2B796427-73F3-481B-866C-FC3D56EAC122}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3984F636-29BC-4CE5-8CF3-2329A9C2A7D2}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{72A35A9F-A175-428E-B2EB-AC78527D302C}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{3FCCC739-2922-4D2F-9DC0-3537F0E5977F}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{CD803C3A-FF96-4FB2-82D8-DF68F7FD4FAF}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6164,7 +6164,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{347ABED6-2FC5-417A-9FCD-CB8FFE53FE87}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{B1B19C0A-7DDB-4C72-962E-11F810EE97D9}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6172,16 +6172,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8146FC52-A477-4479-8B4B-720456989392}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{169E5E8D-C34D-47F5-B252-308C64B2880E}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FD0BC088-CB5A-442E-ACFF-6575CD9C3F67}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{8CFE46F1-75D3-4205-9E55-D423C5463F3F}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C1533A8E-00D9-48AA-BF77-E4DF9ED68F7A}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{4B1B458B-AD21-49F5-8369-2CD9ED4BD265}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D905FCD2-CEB1-4711-A8AA-0770FBC8592D}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{AF4E98C3-D944-414B-AF4E-208AC435F00D}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6190,16 +6190,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{95724543-CBBD-43C1-8D9F-8670C8AF5EC7}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{AC9C6153-67ED-43A0-BB11-3152817F4A35}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{807F0A0D-7729-434A-B81A-37C27B571F26}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{B82FB12E-F809-4A9A-B37A-85414450FA6F}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{509072A7-1958-4360-8769-DDC75F87F211}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{0FD0F4F6-7D42-4B2D-8796-FBB825513B17}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6208,16 +6208,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C812ED3C-8F80-4D22-B6D4-AC035CC2B4D5}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{1164EC0D-8973-4934-B8F1-FE2B07D75D6D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B4613496-7E6F-4194-A901-FC86EBBADB33}" name="Data source">
+    <tableColumn id="1" xr3:uid="{FEDF6BC1-FBEA-43D1-BAB8-589DC6D872BB}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{28219049-A63B-47B1-A48A-916BA0692C82}" name="Data score">
+    <tableColumn id="2" xr3:uid="{79475CCF-6312-464A-BB69-601104A11DDF}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6240,16 +6240,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{655CCD8B-BF0E-4948-A8C5-EE60DFE71239}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{EAACEA5C-382D-4B14-A21A-584728A7A10A}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{36433F79-A4C4-4EB6-BD10-D67BAF3D7A0D}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{1E665611-2A06-4990-943E-3A4799B10AB6}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A1C64A0B-5195-428F-B6F5-8C546D8B057A}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{134E4DE7-4018-49B4-A248-DB8DC2091153}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6258,7 +6258,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{8933C84F-E844-4CD7-A925-692935723E8F}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{4954D004-F7FF-487B-8ECC-8B6762D91454}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6267,19 +6267,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{82A5C969-9C3F-4F73-AC8B-C639D2BDBFB4}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{6A40F661-DD2F-48D3-BEE9-E870DCD60A1F}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AB9501BB-2639-43D6-B68A-79294194505F}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{DA9A0C1F-9EF4-45CB-83CE-2B2305C02ED1}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EFCB2B6D-DE4F-482C-9387-9E8A91B5B8CF}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{962D76BC-C77F-4BA9-B913-0F026AA43412}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{81CE6B4D-17AF-41CF-870D-18D8DAF3CABC}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{A3125B9E-6342-4A8E-8C3E-42B994D345EF}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{18FB9AB9-FDC3-41EA-AC43-6A6CBBE82ED1}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{95E9A13E-A6A1-455A-A238-C6E400DACCB6}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6288,16 +6288,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F47688AB-E0DE-4988-999F-8F08D3561244}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{BA81D7DF-D521-47CD-9997-D2FA82C20439}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{21589287-984E-48C4-943A-79545E6B174C}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{73A046A8-F626-4FF3-907F-4B0DAD89B65D}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8E9CDD17-EE99-4778-B09F-4E0C2FB99750}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EC56680E-26F7-4CD4-9B4E-8D94050B8B3A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6306,16 +6306,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{158328B6-3907-4392-AFC2-F8C4AB7BBB98}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{6BF6CDDB-DBF7-4904-BC00-BEC1CE565B2A}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6A2682B4-C3D3-41B1-A9A5-CD341B338AD2}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{DBA7DA6D-4FD9-48B7-8692-976739B5EBFA}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A75E28E6-0789-4F0F-81F1-A24152E59D86}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8856FD95-9BF9-4137-9F2E-6A19B9836C4C}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6324,16 +6324,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{B7245AEF-8BAD-4F83-B5FE-FA6C33BBCD26}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{2768C421-456F-43F8-B739-653A2BE4EBEA}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B7F13D52-90A1-46F1-AE87-C3A50775031E}" name="Month">
+    <tableColumn id="1" xr3:uid="{1FF9A772-EFFC-444F-BBE8-44684CE6962C}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{18651875-AACE-4C83-82EC-A3F943EFB45C}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{421B5A67-A1A2-4019-8983-556D10F00BD3}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6342,7 +6342,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{E69BCEBA-1BD2-41DB-BC12-595C5098C6D6}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{A0E07D5C-E8D0-4C56-A75B-4F8F7065DEC4}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6362,52 +6362,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{A24B9C52-FFAF-493E-B255-DF0C055293B7}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{56135E2F-47ED-4165-BCE8-E09A9339B6EA}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B432806-D53F-4B46-A933-51812CFD4E94}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4A87C324-8830-481A-BA66-519246FF91B8}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{64223CF6-132B-4BB5-935D-463ED805DB6A}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{98192B9B-A9EF-4BCA-8213-AD89F4FB17D1}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{398F74B0-242B-4BDB-8BE1-EA23C634046B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5DF4811D-6FFB-47B7-9A7A-BD1A91562CF1}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{085C948A-B26D-4F7E-A0BA-D25E0DF8A9C9}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{9C930055-7DE9-48EA-9192-907B77F27A47}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{41D49491-8B7C-4AB1-95F1-B26E9D3666B4}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E7D04A66-911D-48C0-B67E-E2E95C60F3DB}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{58B38240-35E8-4B61-8CAD-C0D8945722E2}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{09CE292C-B840-4D27-8590-8257B11311C1}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B02EF87A-9257-4105-9F8A-B8398BA5C272}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{1227B547-816D-47AC-A539-76F90520D98E}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{06C3FA49-4472-45AF-B982-255330DAAF3F}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{BB1F7993-5EA3-44BA-AD58-97AAE49863D8}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{50E31972-10A3-458E-99D9-A6039185A4C0}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{DB863BF6-1410-4A46-8164-4B2A89B2BDC4}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4FEDC0E7-4585-41D0-9D82-E51CFC16C0AC}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{DED0BC85-C592-41E0-B3A6-CFF080241C64}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4813997B-550E-4DCE-87B4-80A682C2C0DA}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{4306A651-7FD4-4E5E-9FDA-21CC5A7F4900}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F2E360E2-34AD-40DB-93A5-5722025EE092}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{04EBB78D-AEC6-4FC6-9C0E-0A40C564C66F}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{34798E98-3096-45B5-9CD9-6F2AA46F54F2}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{B1AEE62D-B3E4-4300-8533-926546EAB1D2}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C707BBDE-FE68-40C0-8AEC-7E0767B66EEF}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{E101CAF7-41B1-4308-B1E9-17F4ED339B8B}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{44DE0740-88AE-4422-B380-25FA55DF3ABD}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{FC26A283-2E03-4AEC-B940-7DE455FCC417}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6416,16 +6416,16 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{857070AE-A158-45E7-B88D-BD25C5BAF14F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{2CE6C831-099B-49FD-A2C5-4C34BCDB4A39}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{16E298C9-BE0C-4CA4-9612-B74156CF176F}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{225AAD2A-CB71-4DC4-987D-F99C09AD1EEA}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7D2C8B74-D5CB-41CE-BE7A-63ACA70B1F30}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7A889B50-9EC8-44AA-9CB8-C6FD4BE457A4}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18468,7 +18468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6290569-6D3E-4A60-8159-28E6A69C4E62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D75BB2-1C48-48CB-B0A9-6744D232A85A}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22937,19 +22937,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAA